--- a/Issues_No_Tests_new.xlsx
+++ b/Issues_No_Tests_new.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X76"/>
+  <dimension ref="A1:X68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1961,20 +1961,20 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>qgis/QGIS</t>
+          <t>qiskit/qiskit</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>52468</v>
+        <v>1907</v>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>[Geometry Checker Plugin] Minimal polygon area (map units sqr.) doesn't work</t>
+          <t>rzz gate</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/qgis/QGIS/issues/52468</t>
+          <t>https://github.com/Qiskit/qiskit/issues/1907</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1990,19 +1990,17 @@
       <c r="G16" s="3" t="inlineStr"/>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>Plugins
-Regression
-Bug
-Geometry checker</t>
+          <t>bug
+good first issue</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/qgis/QGIS/pull/52476</t>
+          <t>https://github.com/Qiskit/qiskit/pull/1940</t>
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>52476</v>
+        <v>1940</v>
       </c>
       <c r="K16" s="2" t="n"/>
       <c r="L16" s="2" t="n"/>
@@ -2019,7 +2017,7 @@
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>qgsgeometrycheckfactory.cpp changed the configuration for QgsGeometryAreaCheck: it now inserts areaThreshold from ui.doubleSpinBoxArea-&gt;value() instead of ui.doubleSpinBoxAngle-&gt;value(), correcting the parameter wiring for the minimal polygon area check.</t>
+          <t>The PR changes the rzz gate decomposition from applying U1Gate to the control qubit to applying it to the target qubit (U1Gate(self.params[0], q[0]) -&gt; U1Gate(self.params[0], q[1])), matching the expected behavior stated in the issue and indicated by the PR title/body and changelog entry.</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2030,52 +2028,52 @@
       <c r="R16" s="3" t="inlineStr"/>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t>The fix directly corrects the wrong UI value feeding the area-threshold parameter, which matches the described symptom that the search results do not correspond to the spinbox value for minimal polygon area.</t>
+          <t>The implementation directly updates the rzz decomposition to place the U1 phase on the target qubit rather than the control, which addresses the described incorrect behavior mechanism.</t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t>Geographical Information Science</t>
+          <t>Physics</t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t>swe_dominant</t>
+          <t>science_dominant</t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="W16" s="3" t="inlineStr">
+        <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="W16" s="3" t="inlineStr">
-        <is>
-          <t>easy</t>
-        </is>
-      </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t>insufficient</t>
+          <t>sufficient</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>qiskit/qiskit</t>
+          <t>openmm/openmm</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>1907</v>
+        <v>161</v>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>rzz gate</t>
+          <t>ZeroDivisionError: float division by zero</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/Qiskit/qiskit/issues/1907</t>
+          <t>https://github.com/openmm/pdbfixer/issues/161</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -2089,19 +2087,14 @@
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr"/>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>bug
-good first issue</t>
-        </is>
-      </c>
+      <c r="H17" s="3" t="inlineStr"/>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/Qiskit/qiskit/pull/1940</t>
+          <t>https://github.com/openmm/openmm/pull/2038</t>
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>1940</v>
+        <v>2038</v>
       </c>
       <c r="K17" s="2" t="n"/>
       <c r="L17" s="2" t="n"/>
@@ -2118,7 +2111,7 @@
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>The PR changes the rzz gate decomposition from applying U1Gate to the control qubit to applying it to the target qubit (U1Gate(self.params[0], q[0]) -&gt; U1Gate(self.params[0], q[1])), matching the expected behavior stated in the issue and indicated by the PR title/body and changelog entry.</t>
+          <t>In modeller.py addMembrane, proteinMinPos/proteinMaxPos were corrected to compute per-coordinate minima/maxima across proteinPos instead of using Python min/max on Vec3 objects, which could yield an incorrect proteinSize (and thus zero vectors leading to division by zero when computing invBox).</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2129,22 +2122,22 @@
       <c r="R17" s="3" t="inlineStr"/>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t>The implementation directly updates the rzz decomposition to place the U1 phase on the target qubit rather than the control, which addresses the described incorrect behavior mechanism.</t>
+          <t>The patch changes the membrane bounding-box calculation to be coordinate-correct, which plausibly prevents the zero box dimension that caused the float division by zero in invBox.</t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t>Physics</t>
+          <t>Biology</t>
         </is>
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t>science_dominant</t>
+          <t>swe_dominant</t>
         </is>
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>easy</t>
         </is>
       </c>
       <c r="W17" s="3" t="inlineStr">
@@ -2154,27 +2147,27 @@
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t>sufficient</t>
+          <t>insufficient</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>qgis/QGIS</t>
+          <t>qutip/qutip</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>52189</v>
+        <v>2520</v>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Global Map Shading z factor value doesn't display properly and doesn't persist</t>
+          <t>Shifted Drude-Lorentz bath for HEOM solver</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/qgis/QGIS/issues/52189</t>
+          <t>https://github.com/qutip/qutip/issues/2520</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -2189,22 +2182,21 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>https://user-images.githubusercontent.com/1100600/224539169-72bd7959-6d1a-4419-9d3d-80d23f48ff99.png</t>
+          <t>https://github.com/user-attachments/assets/cece04e7-59c9-44ad-9b33-143942fc4093</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>3D
-Bug</t>
+          <t>ENH</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/qgis/QGIS/pull/52213</t>
+          <t>https://github.com/qutip/qutip/pull/2574</t>
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>52213</v>
+        <v>2574</v>
       </c>
       <c r="K18" s="2" t="n"/>
       <c r="L18" s="2" t="n"/>
@@ -2221,7 +2213,7 @@
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>The PR changes serialization of hillshading-z-factor (and related doubles) to use qgsDoubleToString during writeXml, and increases the UI spinbox decimals to 6 for z-factor input, directly addressing loss/rounding of small Z values and non-persistence when other settings trigger renderer reconfiguration.</t>
+          <t>The PR patch excerpt modifies the Padé bath correlation coefficient handling by no longer discarding the real/imaginary structure of the complex eta; specifically it changes ck_real/vk_real computation to use _corr outputs directly (removing np.real-only behavior and setting ck_imag/vk_imag analytically) and also removes the '-1.0j' term from eta_p so the imaginary-part bookkeeping matches the shifted Drude-Lorentz construction. Corresponding documentation and guide updates describe constructing shifted Drude-Lorentz environments via summing two Drude-Lorentz baths with gamma -&gt; gamma ± i Omega.</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2232,52 +2224,52 @@
       <c r="R18" s="3" t="inlineStr"/>
       <c r="S18" s="3" t="inlineStr">
         <is>
-          <t>By ensuring double precision values like 0.00001 are written and restored with sufficient textual precision and by allowing the UI to accept/display that precision, the fix targets the numerical representation/persistence failure described for the Z Factor.</t>
+          <t>The code changes in the Padé environment/bath correlation parameter computation remove the incorrect real-part projection and restore correct handling of complex gamma/eta, which is precisely what the issue identifies as causing the shifted Drude-Lorentz mismatch between implementations.</t>
         </is>
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t>Geographical Information Science</t>
+          <t>Physics</t>
         </is>
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t>swe_dominant</t>
+          <t>science_dominant</t>
         </is>
       </c>
       <c r="V18" s="3" t="inlineStr">
         <is>
-          <t>easy</t>
+          <t>hard</t>
         </is>
       </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t>easy</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t>insufficient</t>
+          <t>sufficient</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>openmm/openmm</t>
+          <t>yt-project/yt</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>161</v>
+        <v>5220</v>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>ZeroDivisionError: float division by zero</t>
+          <t>BUG: partition_index_2d needs some updates</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/openmm/pdbfixer/issues/161</t>
+          <t>https://github.com/yt-project/yt/issues/5220</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -2294,11 +2286,11 @@
       <c r="H19" s="3" t="inlineStr"/>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/openmm/openmm/pull/2038</t>
+          <t>https://github.com/yt-project/yt/pull/5221</t>
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>2038</v>
+        <v>5221</v>
       </c>
       <c r="K19" s="2" t="n"/>
       <c r="L19" s="2" t="n"/>
@@ -2315,7 +2307,7 @@
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t>In modeller.py addMembrane, proteinMinPos/proteinMaxPos were corrected to compute per-coordinate minima/maxima across proteinPos instead of using Python min/max on Vec3 objects, which could yield an incorrect proteinSize (and thus zero vectors leading to division by zero when computing invBox).</t>
+          <t>The PR changes partition_index_2d to use a locally available center attribute (falling back to ds.domain_center) and to call ds.region with that computed center, aligning the partition-region construction with the current ds.region usage expectations.</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2326,12 +2318,12 @@
       <c r="R19" s="3" t="inlineStr"/>
       <c r="S19" s="3" t="inlineStr">
         <is>
-          <t>The patch changes the membrane bounding-box calculation to be coordinate-correct, which plausibly prevents the zero box dimension that caused the float division by zero in invBox.</t>
+          <t>The failure reported as outdated center handling is directly addressed by updating partition_index_2d to consistently pass the appropriate center into ds.region and grid_collection.</t>
         </is>
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t>Biology</t>
+          <t>Astronomy</t>
         </is>
       </c>
       <c r="U19" s="3" t="inlineStr">
@@ -2346,7 +2338,7 @@
       </c>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t>easy</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="X19" s="3" t="inlineStr">
@@ -2358,20 +2350,20 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>qutip/qutip</t>
+          <t>samtools/samtools</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>2520</v>
+        <v>2095</v>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Shifted Drude-Lorentz bath for HEOM solver</t>
+          <t>Consensus generation using quality at high depth fails</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/qutip/qutip/issues/2520</t>
+          <t>https://github.com/samtools/samtools/issues/2095</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2381,26 +2373,18 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t>https://github.com/user-attachments/assets/cece04e7-59c9-44ad-9b33-143942fc4093</t>
-        </is>
-      </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>ENH</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr"/>
+      <c r="H20" s="3" t="inlineStr"/>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/qutip/qutip/pull/2574</t>
+          <t>https://github.com/samtools/samtools/pull/2099</t>
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>2574</v>
+        <v>2099</v>
       </c>
       <c r="K20" s="2" t="n"/>
       <c r="L20" s="2" t="n"/>
@@ -2417,7 +2401,7 @@
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t>The PR patch excerpt modifies the Padé bath correlation coefficient handling by no longer discarding the real/imaginary structure of the complex eta; specifically it changes ck_real/vk_real computation to use _corr outputs directly (removing np.real-only behavior and setting ck_imag/vk_imag analytically) and also removes the '-1.0j' term from eta_p so the imaginary-part bookkeeping matches the shifted Drude-Lorentz construction. Corresponding documentation and guide updates describe constructing shifted Drude-Lorentz environments via summing two Drude-Lorentz baths with gamma -&gt; gamma ± i Omega.</t>
+          <t>The issue report and comments attribute the consensus failure at very high depth to 32-bit integer overflow when summing quality values, and the PR changes switch the quality-accumulation variables in calculate_consensus_simple from int to uint64_t (including tscore/score1/score2/used_score), which prevents that overflow.</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2428,22 +2412,22 @@
       <c r="R20" s="3" t="inlineStr"/>
       <c r="S20" s="3" t="inlineStr">
         <is>
-          <t>The code changes in the Padé environment/bath correlation parameter computation remove the incorrect real-part projection and restore correct handling of complex gamma/eta, which is precisely what the issue identifies as causing the shifted Drude-Lorentz mismatch between implementations.</t>
+          <t>The fix directly changes the overflow-prone quality-summation accumulators from 32-bit int to 64-bit uint64_t in the exact consensus calculation path described, plausibly eliminating the observed high-depth consensus breakage.</t>
         </is>
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t>Physics</t>
+          <t>Bioinformatics</t>
         </is>
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t>science_dominant</t>
+          <t>swe_dominant</t>
         </is>
       </c>
       <c r="V20" s="3" t="inlineStr">
         <is>
-          <t>hard</t>
+          <t>easy</t>
         </is>
       </c>
       <c r="W20" s="3" t="inlineStr">
@@ -2453,27 +2437,27 @@
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t>sufficient</t>
+          <t>insufficient</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>yt-project/yt</t>
+          <t>mne-tools/mne-python</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>5220</v>
+        <v>13122</v>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>BUG: partition_index_2d needs some updates</t>
+          <t>Insufficiently sensitive head movement detection for chpi extraction?</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/yt-project/yt/issues/5220</t>
+          <t>https://github.com/mne-tools/mne-python/issues/13122</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -2490,11 +2474,11 @@
       <c r="H21" s="3" t="inlineStr"/>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/yt-project/yt/pull/5221</t>
+          <t>https://github.com/mne-tools/mne-python/pull/13123</t>
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>5221</v>
+        <v>13123</v>
       </c>
       <c r="K21" s="2" t="n"/>
       <c r="L21" s="2" t="n"/>
@@ -2511,7 +2495,7 @@
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t>The PR changes partition_index_2d to use a locally available center attribute (falling back to ds.domain_center) and to call ds.region with that computed center, aligning the partition-region construction with the current ds.region usage expectations.</t>
+          <t>The implementation changed the detection condition from requiring all coordinate differences to be nonzero (np.all over np.diff(..., axis=1)) to requiring any coordinate difference to be nonzero (np.any over np.diff(..., axis=1)) when computing indices of CTF cHPI location changes in mne/chpi.py.</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2522,52 +2506,52 @@
       <c r="R21" s="3" t="inlineStr"/>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t>The failure reported as outdated center handling is directly addressed by updating partition_index_2d to consistently pass the appropriate center into ds.region and grid_collection.</t>
+          <t>Changing np.all to np.any in the index-finding logic directly addresses the mechanism that previously missed head movement unless every HPI coil coordinate changed between samples.</t>
         </is>
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t>Astronomy</t>
+          <t>Neuroscience</t>
         </is>
       </c>
       <c r="U21" s="3" t="inlineStr">
         <is>
-          <t>swe_dominant</t>
+          <t>joint</t>
         </is>
       </c>
       <c r="V21" s="3" t="inlineStr">
         <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="W21" s="3" t="inlineStr">
+        <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="W21" s="3" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t>insufficient</t>
+          <t>sufficient</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>fenics/dolfinx</t>
+          <t>lammps/lammps</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>1257</v>
+        <v>3627</v>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>assemble_interior_facets not using block size for RHS assembly</t>
+          <t>[BUG] compute chunk/atom chunk IDs are not stable on step 0 of multi-runs with "ids once"</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/FEniCS/dolfinx/issues/1257</t>
+          <t>https://github.com/lammps/lammps/issues/3627</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -2581,14 +2565,18 @@
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr"/>
-      <c r="H22" s="3" t="inlineStr"/>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/FEniCS/dolfinx/pull/1264</t>
+          <t>https://github.com/lammps/lammps/pull/3699</t>
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>1264</v>
+        <v>3699</v>
       </c>
       <c r="K22" s="2" t="n"/>
       <c r="L22" s="2" t="n"/>
@@ -2605,7 +2593,7 @@
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t>The change in assemble_interior_facets adds bs=dofmap.bs(), allocates be with size bs*(dmap0.rows()+dmap1.rows()), initializes it, and accumulates into b using bs-strided indexing b[bs*dmap[i]+k] += be[...], which corrects RHS assembly to respect the block size for vector-valued DOFs on interior facets.</t>
+          <t>The patch changes ComputeChunkAtom::compute_ichunk() so that when idsflag==ONCE and previous chunk IDs were stored (restore path), it does not incorrectly reset invoked_ichunk for the ONCE case (it only updates invoked_ichunk for the NFREQ restore case), preventing re-computation of chunk IDs at the beginning of subsequent runs.</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2616,12 +2604,12 @@
       <c r="R22" s="3" t="inlineStr"/>
       <c r="S22" s="3" t="inlineStr">
         <is>
-          <t>The patch explicitly updates interior-facet RHS assembly to allocate and scatter contributions using the dofmap block size, addressing the mechanism described in the issue.</t>
+          <t>The code change directly addresses the reported failure mode by ensuring that ONCE chunk IDs are restored from fixstore on subsequent runs rather than triggering unintended recalculation at step 0.</t>
         </is>
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t>Mathematics</t>
+          <t>Materials Science</t>
         </is>
       </c>
       <c r="U22" s="3" t="inlineStr">
@@ -2636,7 +2624,7 @@
       </c>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t>hard</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="X22" s="3" t="inlineStr">
@@ -2648,20 +2636,20 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>samtools/samtools</t>
+          <t>sunpy/sunpy</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>2095</v>
+        <v>4258</v>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Consensus generation using quality at high depth fails</t>
+          <t>submap inverted rectangle warning fires when not expected</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/samtools/samtools/issues/2095</t>
+          <t>https://github.com/sunpy/sunpy/issues/4258</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -2678,11 +2666,11 @@
       <c r="H23" s="3" t="inlineStr"/>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/samtools/samtools/pull/2099</t>
+          <t>https://github.com/sunpy/sunpy/pull/4260</t>
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>2099</v>
+        <v>4260</v>
       </c>
       <c r="K23" s="2" t="n"/>
       <c r="L23" s="2" t="n"/>
@@ -2699,7 +2687,7 @@
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t>The issue report and comments attribute the consensus failure at very high depth to 32-bit integer overflow when summing quality values, and the PR changes switch the quality-accumulation variables in calculate_consensus_simple from int to uint64_t (including tscore/score1/score2/used_score), which prevents that overflow.</t>
+          <t>In sunpy/map/mapbase.py, submap’s y-pixel ordering used [top_right[1], bottom_left[1]], which can invert the rectangle and trigger the “inverted in the left/right direction” warning; the fix swaps it to [bottom_left[1], top_right[1]], aligning the y-range with the intended bottom/top semantics for the rectangle check.</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2710,12 +2698,12 @@
       <c r="R23" s="3" t="inlineStr"/>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t>The fix directly changes the overflow-prone quality-summation accumulators from 32-bit int to 64-bit uint64_t in the exact consensus calculation path described, plausibly eliminating the observed high-depth consensus breakage.</t>
+          <t>The mechanism for the warning is incorrect y-pixel ordering when forming the rectangle pixel bounds, and the PR directly corrects that ordering so the rectangle is no longer misdetected as inverted.</t>
         </is>
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t>Bioinformatics</t>
+          <t>Astronomy</t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
@@ -2730,7 +2718,7 @@
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>easy</t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
@@ -2742,41 +2730,53 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>mne-tools/mne-python</t>
+          <t>yt-project/yt</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>13122</v>
+        <v>3554</v>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Insufficiently sensitive head movement detection for chpi extraction?</t>
+          <t>BUG: matplotlib 3.5 breaks colorbars</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/mne-tools/mne-python/issues/13122</t>
+          <t>https://github.com/yt-project/yt/issues/3554</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1,2</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr"/>
-      <c r="H24" s="3" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>https://user-images.githubusercontent.com/14075922/136946868-7a42daa4-6328-4ea4-b3b2-9f42d8818010.png
+https://user-images.githubusercontent.com/14075922/136946793-d353ca53-d19e-4a60-a9a4-dbc4eac71bce.png
+https://user-images.githubusercontent.com/14075922/136991548-e0469308-6906-4429-9d9b-d4bfb983e96e.png
+https://user-images.githubusercontent.com/14075922/136995481-00412e5f-a97d-4214-8075-a2e68840d970.png</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>bug
+viz: 2D</t>
+        </is>
+      </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/mne-tools/mne-python/pull/13123</t>
+          <t>https://github.com/yt-project/yt/pull/3556</t>
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>13123</v>
+        <v>3556</v>
       </c>
       <c r="K24" s="2" t="n"/>
       <c r="L24" s="2" t="n"/>
@@ -2793,7 +2793,7 @@
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t>The implementation changed the detection condition from requiring all coordinate differences to be nonzero (np.all over np.diff(..., axis=1)) to requiring any coordinate difference to be nonzero (np.any over np.diff(..., axis=1)) when computing indices of CTF cHPI location changes in mne/chpi.py.</t>
+          <t>The reported mechanism is matplotlib 3.5 colorbar tick/label behavior breaking for symlog-like normalization; the closing PR changes yt’s symlog colorbar tick handling to account for matplotlib versions (using 3.5.0b boundary) and adjusts tick generation/minor-tick behavior in the symlog path (base_plot_types, plot_container, plot_window), which is directly relevant to colorbar tick/color normalization discrepancies described in the bug report and existing workaround for symlog tick issues.</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -2804,52 +2804,52 @@
       <c r="R24" s="3" t="inlineStr"/>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t>Changing np.all to np.any in the index-finding logic directly addresses the mechanism that previously missed head movement unless every HPI coil coordinate changed between samples.</t>
+          <t>The PR explicitly updates yt’s symlog colorbar tick/minor-tick and normalization logic with matplotlib 3.5-specific handling, matching the bug’s described colorbar/tick regression mechanism.</t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t>Neuroscience</t>
+          <t>Astronomy</t>
         </is>
       </c>
       <c r="U24" s="3" t="inlineStr">
         <is>
-          <t>joint</t>
+          <t>swe_dominant</t>
         </is>
       </c>
       <c r="V24" s="3" t="inlineStr">
         <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="W24" s="3" t="inlineStr">
+        <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="W24" s="3" t="inlineStr">
-        <is>
-          <t>easy</t>
-        </is>
-      </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t>sufficient</t>
+          <t>insufficient</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>lammps/lammps</t>
+          <t>yt-project/yt</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>3627</v>
+        <v>3531</v>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>[BUG] compute chunk/atom chunk IDs are not stable on step 0 of multi-runs with "ids once"</t>
+          <t>BUG: wrong axis labels representation in SlicePlot for spherical data</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/lammps/lammps/issues/3627</t>
+          <t>https://github.com/yt-project/yt/issues/3531</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -2859,22 +2859,29 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>https://user-images.githubusercontent.com/14075922/134900776-771c7787-44cb-4751-9a16-b06432be46f3.png
+https://user-images.githubusercontent.com/14075922/134901098-a37df2fa-3b1e-4d8f-aebb-a9c3c5197864.png</t>
+        </is>
+      </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>bug</t>
+          <t>bug
+viz: 2D
+coordinates: non-cartesian</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/lammps/lammps/pull/3699</t>
+          <t>https://github.com/yt-project/yt/pull/3532</t>
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>3699</v>
+        <v>3532</v>
       </c>
       <c r="K25" s="2" t="n"/>
       <c r="L25" s="2" t="n"/>
@@ -2891,7 +2898,7 @@
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t>The patch changes ComputeChunkAtom::compute_ichunk() so that when idsflag==ONCE and previous chunk IDs were stored (restore path), it does not incorrectly reset invoked_ichunk for the ONCE case (it only updates invoked_ichunk for the NFREQ restore case), preventing re-computation of chunk IDs at the beginning of subsequent runs.</t>
+          <t>The reported mechanism is incorrect default axis-label glyphs for SlicePlot when slicing along the spherical 'r' direction. The code change updates spherical_coordinates.py image_axis_name mapping for axis_id['r'] from ('theta','phi') to ('\\theta','\\phi'), aligning label rendering with the expected LaTeX theta/phi glyphs.</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -2902,73 +2909,83 @@
       <c r="R25" s="3" t="inlineStr"/>
       <c r="S25" s="3" t="inlineStr">
         <is>
-          <t>The code change directly addresses the reported failure mode by ensuring that ONCE chunk IDs are restored from fixstore on subsequent runs rather than triggering unintended recalculation at step 0.</t>
+          <t>The fix directly replaces the plain-text 'theta'/'phi' label tokens with LaTeX '\theta'/'\phi' for the spherical 'r' axis label mapping, which matches the requested behavior for SlicePlot spherical data.</t>
         </is>
       </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t>Materials Science</t>
+          <t>Astronomy</t>
         </is>
       </c>
       <c r="U25" s="3" t="inlineStr">
         <is>
-          <t>joint</t>
+          <t>swe_dominant</t>
         </is>
       </c>
       <c r="V25" s="3" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>easy</t>
         </is>
       </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>easy</t>
         </is>
       </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t>sufficient</t>
+          <t>insufficient</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>sunpy/sunpy</t>
+          <t>yt-project/yt</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>4258</v>
+        <v>2127</v>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>submap inverted rectangle warning fires when not expected</t>
+          <t>Wrong units for sphere radius</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/sunpy/sunpy/issues/4258</t>
+          <t>https://github.com/yt-project/yt/issues/2127</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G26" s="3" t="inlineStr"/>
-      <c r="H26" s="3" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>https://user-images.githubusercontent.com/5411875/50823314-f9664600-1333-11e9-9a99-8745902fa8b7.png
+https://user-images.githubusercontent.com/5411875/50823316-f9664600-1333-11e9-81ee-95eeeb1d98ef.png</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>bug
+new contributor friendly</t>
+        </is>
+      </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/sunpy/sunpy/pull/4260</t>
+          <t>https://github.com/yt-project/yt/pull/2128</t>
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>4260</v>
+        <v>2128</v>
       </c>
       <c r="K26" s="2" t="n"/>
       <c r="L26" s="2" t="n"/>
@@ -2985,7 +3002,7 @@
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t>In sunpy/map/mapbase.py, submap’s y-pixel ordering used [top_right[1], bottom_left[1]], which can invert the rectangle and trigger the “inverted in the left/right direction” warning; the fix swaps it to [bottom_left[1], top_right[1]], aligning the y-range with the intended bottom/top semantics for the rectangle check.</t>
+          <t>The reported fix modifies plot_modifications.py to convert a YTQuantity `radius` into the same units as `center` (or `code_length` if `center` is not a YTArray), addressing the unit mismatch shown in the reproduction (sphere annotation only works when radius is manually converted).</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -2996,7 +3013,7 @@
       <c r="R26" s="3" t="inlineStr"/>
       <c r="S26" s="3" t="inlineStr">
         <is>
-          <t>The mechanism for the warning is incorrect y-pixel ordering when forming the rectangle pixel bounds, and the PR directly corrects that ordering so the rectangle is no longer misdetected as inverted.</t>
+          <t>By converting `radius` to the `center` units at the annotation call site, the implementation aligns radius and center spatial units, addressing the mismatch demonstrated by the base vs expected images.</t>
         </is>
       </c>
       <c r="T26" s="3" t="inlineStr">
@@ -3028,20 +3045,20 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>sunpy/sunpy</t>
+          <t>yt-project/yt</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>1478</v>
+        <v>2408</v>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>EIT data fails with wcsaxes</t>
+          <t>sliceplot data range ignored when log with negative data</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/sunpy/sunpy/issues/1478</t>
+          <t>https://github.com/yt-project/yt/issues/2408</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -3057,16 +3074,18 @@
       <c r="G27" s="3" t="inlineStr"/>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>Affects Dev</t>
+          <t>bug
+viz: 2D
+proposal</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/sunpy/sunpy/pull/1505</t>
+          <t>https://github.com/yt-project/yt/pull/2485</t>
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>1505</v>
+        <v>2485</v>
       </c>
       <c r="K27" s="2" t="n"/>
       <c r="L27" s="2" t="n"/>
@@ -3083,7 +3102,7 @@
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t>The closing PR adds a coordinate type check and forces longitude/latitude coord types on wcsaxes grid axes, addressing the reported mechanism that EIT WCS celestial axes are not correctly recognized as angular axes by wcsaxes/wcslib so arcsecond formatting fails; the change is directly at default_wcs_grid where tick/formatter behavior is set.</t>
+          <t>PR change in yt/visualization/plot_container.py modifies set_zlim so that when computed zmin is positive and the current field transform is symlog_transform, it switches to log_transform before assigning zmin/zmax.</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3094,7 +3113,7 @@
       <c r="R27" s="3" t="inlineStr"/>
       <c r="S27" s="3" t="inlineStr">
         <is>
-          <t>By correcting the coord_type used for the wcsaxes grid axes to longitude/latitude when needed, the patch aligns axis semantics with what wcsaxes expects for proper angular tick formatting, plausibly fixing the EIT WCS arcsecond formatting failure described.</t>
+          <t>If the user sets zmin&gt;0 and the transform is symlog due to unrelated negative values elsewhere, switching to log_transform ensures the zlim range is respected for the positive-only range.</t>
         </is>
       </c>
       <c r="T27" s="3" t="inlineStr">
@@ -3104,12 +3123,12 @@
       </c>
       <c r="U27" s="3" t="inlineStr">
         <is>
-          <t>joint</t>
+          <t>swe_dominant</t>
         </is>
       </c>
       <c r="V27" s="3" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>easy</t>
         </is>
       </c>
       <c r="W27" s="3" t="inlineStr">
@@ -3119,60 +3138,52 @@
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t>sufficient</t>
+          <t>insufficient</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>yt-project/yt</t>
+          <t>mne-tools/mne-python</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>3554</v>
+        <v>9454</v>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>BUG: matplotlib 3.5 breaks colorbars</t>
+          <t>Dropping epochs with Epochs.plot() not working properly</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/yt-project/yt/issues/3554</t>
+          <t>https://github.com/mne-tools/mne-python/issues/9454</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G28" s="3" t="inlineStr">
-        <is>
-          <t>https://user-images.githubusercontent.com/14075922/136946868-7a42daa4-6328-4ea4-b3b2-9f42d8818010.png
-https://user-images.githubusercontent.com/14075922/136946793-d353ca53-d19e-4a60-a9a4-dbc4eac71bce.png
-https://user-images.githubusercontent.com/14075922/136991548-e0469308-6906-4429-9d9b-d4bfb983e96e.png
-https://user-images.githubusercontent.com/14075922/136995481-00412e5f-a97d-4214-8075-a2e68840d970.png</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr"/>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>bug
-viz: 2D</t>
+          <t>BUG</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/yt-project/yt/pull/3556</t>
+          <t>https://github.com/mne-tools/mne-python/pull/9459</t>
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>3556</v>
+        <v>9459</v>
       </c>
       <c r="K28" s="2" t="n"/>
       <c r="L28" s="2" t="n"/>
@@ -3189,7 +3200,7 @@
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t>The reported mechanism is matplotlib 3.5 colorbar tick/label behavior breaking for symlog-like normalization; the closing PR changes yt’s symlog colorbar tick handling to account for matplotlib versions (using 3.5.0b boundary) and adjusts tick generation/minor-tick behavior in the symlog path (base_plot_types, plot_container, plot_window), which is directly relevant to colorbar tick/color normalization discrepancies described in the bug report and existing workaround for symlog tick issues.</t>
+          <t>The changes in mne/viz/_figure.py adjust how epochs are indexed and how bad-epoch highlighting colors are mapped during scrolling/drawing: (1) compute sampling_period from inst.times and use it to subtract one sample before searchsorted for t_start to avoid boundary-time precision misalignment; (2) fix a bug where the horizontal scroll boundary patch width incorrectly used boundary_times[:2] rather than boundary_times[ix:ix+2]; (3) change visible bad-epoch mapping from values to indices (visible_bad_epoch_ix) so the override of bad-epoch colors applies to the correct epoch columns after recomputation during scroll/redraw.</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3200,12 +3211,12 @@
       <c r="R28" s="3" t="inlineStr"/>
       <c r="S28" s="3" t="inlineStr">
         <is>
-          <t>The PR explicitly updates yt’s symlog colorbar tick/minor-tick and normalization logic with matplotlib 3.5-specific handling, matching the bug’s described colorbar/tick regression mechanism.</t>
+          <t>By correcting boundary-time indexing precision and using correct epoch index mapping when drawing, the PR addresses the reported scroll/redraw mismatch where selection and dropped/highlighted epochs become inconsistent.</t>
         </is>
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t>Astronomy</t>
+          <t>Neuroscience</t>
         </is>
       </c>
       <c r="U28" s="3" t="inlineStr">
@@ -3232,20 +3243,20 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>yt-project/yt</t>
+          <t>nilearn/nilearn</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>3531</v>
+        <v>2705</v>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>BUG: wrong axis labels representation in SlicePlot for spherical data</t>
+          <t>Possible identical design matrix columns with generate_fake_fmri_data_and_design</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/yt-project/yt/issues/3531</t>
+          <t>https://github.com/nilearn/nilearn/issues/2705</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -3255,29 +3266,18 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G29" s="3" t="inlineStr">
-        <is>
-          <t>https://user-images.githubusercontent.com/14075922/134900776-771c7787-44cb-4751-9a16-b06432be46f3.png
-https://user-images.githubusercontent.com/14075922/134901098-a37df2fa-3b1e-4d8f-aebb-a9c3c5197864.png</t>
-        </is>
-      </c>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t>bug
-viz: 2D
-coordinates: non-cartesian</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr"/>
+      <c r="H29" s="3" t="inlineStr"/>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/yt-project/yt/pull/3532</t>
+          <t>https://github.com/nilearn/nilearn/pull/2706</t>
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>3532</v>
+        <v>2706</v>
       </c>
       <c r="K29" s="2" t="n"/>
       <c r="L29" s="2" t="n"/>
@@ -3294,7 +3294,7 @@
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t>The reported mechanism is incorrect default axis-label glyphs for SlicePlot when slicing along the spherical 'r' direction. The code change updates spherical_coordinates.py image_axis_name mapping for axis_id['r'] from ('theta','phi') to ('\\theta','\\phi'), aligning label rendering with the expected LaTeX theta/phi glyphs.</t>
+          <t>The patch changes generate_fake_fmri_data_and_design to sample column labels with replace=False instead of the previous default sampling with replacement, preventing duplicate column names (e.g., 'a-a') that can make contrast computations degenerate.</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       <c r="R29" s="3" t="inlineStr"/>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t>The fix directly replaces the plain-text 'theta'/'phi' label tokens with LaTeX '\theta'/'\phi' for the spherical 'r' axis label mapping, which matches the requested behavior for SlicePlot spherical data.</t>
+          <t>Sampling without replacement directly removes the mechanism that produced identically named design-matrix columns, addressing the random contrast failure.</t>
         </is>
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t>Astronomy</t>
+          <t>Neuroscience</t>
         </is>
       </c>
       <c r="U29" s="3" t="inlineStr">
@@ -3337,25 +3337,25 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>yt-project/yt</t>
+          <t>nilearn/nilearn</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>2127</v>
+        <v>2430</v>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Wrong units for sphere radius</t>
+          <t>Incorrect colorbar with thresholded statmap</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/yt-project/yt/issues/2127</t>
+          <t>https://github.com/nilearn/nilearn/issues/2430</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1,2</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -3365,23 +3365,18 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>https://user-images.githubusercontent.com/5411875/50823314-f9664600-1333-11e9-9a99-8745902fa8b7.png
-https://user-images.githubusercontent.com/5411875/50823316-f9664600-1333-11e9-81ee-95eeeb1d98ef.png</t>
-        </is>
-      </c>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t>bug
-new contributor friendly</t>
-        </is>
-      </c>
+          <t>https://user-images.githubusercontent.com/54182/80816934-714a2680-8b9e-11ea-8e43-b240ead33bd5.png
+https://user-images.githubusercontent.com/54182/80817874-39dc7980-8ba0-11ea-82fd-7979f88d429f.png</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr"/>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/yt-project/yt/pull/2128</t>
+          <t>https://github.com/nilearn/nilearn/pull/2431</t>
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>2128</v>
+        <v>2431</v>
       </c>
       <c r="K30" s="2" t="n"/>
       <c r="L30" s="2" t="n"/>
@@ -3398,7 +3393,7 @@
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t>The reported fix modifies plot_modifications.py to convert a YTQuantity `radius` into the same units as `center` (or `code_length` if `center` is not a YTArray), addressing the unit mismatch shown in the reproduction (sphere annotation only works when radius is manually converted).</t>
+          <t>The PR modifies nilearn/plotting/img_plotting.py _crop_colorbar to handle Matplotlib &gt;=3.2.0 by setting the colorbar axis limits with the un-normalized cbar_vmin/cbar_vmax and recomputing the outline via cbar._mesh()/cbar._outline, while keeping the previous cbar.norm-based logic for older Matplotlib versions; this directly addresses the reported mechanism where colorbars were incorrectly scaled between 0 and 1 after a Matplotlib API change.</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3409,12 +3404,12 @@
       <c r="R30" s="3" t="inlineStr"/>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t>By converting `radius` to the `center` units at the annotation call site, the implementation aligns radius and center spatial units, addressing the mismatch demonstrated by the base vs expected images.</t>
+          <t>Because the fix changes the colorbar cropping logic to use the correct axis scaling depending on the Matplotlib version, it plausibly restores the intended correspondence between thresholded statmap values and the colorbar range.</t>
         </is>
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t>Astronomy</t>
+          <t>Neuroscience</t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
@@ -3429,7 +3424,7 @@
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t>easy</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
@@ -3441,20 +3436,20 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>yt-project/yt</t>
+          <t>lammps/lammps</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>2408</v>
+        <v>2175</v>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>sliceplot data range ignored when log with negative data</t>
+          <t>[BUG] Pressure offset in NPT run with GPU accelerated TIP4P</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/yt-project/yt/issues/2408</t>
+          <t>https://github.com/lammps/lammps/issues/2175</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -3464,24 +3459,22 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G31" s="3" t="inlineStr"/>
-      <c r="H31" s="3" t="inlineStr">
-        <is>
-          <t>bug
-viz: 2D
-proposal</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>https://user-images.githubusercontent.com/19315755/85327891-95323600-b484-11ea-8777-84fd2552c1f1.png</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr"/>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/yt-project/yt/pull/2485</t>
+          <t>https://github.com/lammps/lammps/pull/2187</t>
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>2485</v>
+        <v>2187</v>
       </c>
       <c r="K31" s="2" t="n"/>
       <c r="L31" s="2" t="n"/>
@@ -3498,7 +3491,7 @@
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t>PR change in yt/visualization/plot_container.py modifies set_zlim so that when computed zmin is positive and the current field transform is symlog_transform, it switches to log_transform before assigning zmin/zmax.</t>
+          <t>The fix changes GPU TIP4P virial accumulation logic in the exact code path reported by the issue (`lib/gpu/lal_lj_tip4p_long.cu`) and updates the GPU pair wrapper to initialize energy/virial bookkeeping correctly; the PR body explicitly states it fixes incorrect virial accumulation for `eflag == 0, vflag == 1`, matching the reported pressure offset in NPT GPU TIP4P runs.</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3509,52 +3502,52 @@
       <c r="R31" s="3" t="inlineStr"/>
       <c r="S31" s="3" t="inlineStr">
         <is>
-          <t>If the user sets zmin&gt;0 and the transform is symlog due to unrelated negative values elsewhere, switching to log_transform ensures the zlim range is respected for the positive-only range.</t>
+          <t>The change directly addresses the GPU TIP4P virial/pressure computation path that caused the reported pressure offset, so it is a relevant direct fix.</t>
         </is>
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t>Astronomy</t>
+          <t>Materials Science</t>
         </is>
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t>swe_dominant</t>
+          <t>joint</t>
         </is>
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t>easy</t>
+          <t>hard</t>
         </is>
       </c>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t>easy</t>
+          <t>hard</t>
         </is>
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t>insufficient</t>
+          <t>sufficient</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>mne-tools/mne-python</t>
+          <t>lammps/lammps</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>9454</v>
+        <v>2178</v>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>Dropping epochs with Epochs.plot() not working properly</t>
+          <t>[BUG] Accuracy regression in MSM</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/mne-tools/mne-python/issues/9454</t>
+          <t>https://github.com/lammps/lammps/issues/2178</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -3570,16 +3563,16 @@
       <c r="G32" s="3" t="inlineStr"/>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>bug</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/mne-tools/mne-python/pull/9459</t>
+          <t>https://github.com/lammps/lammps/pull/2181</t>
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>9459</v>
+        <v>2181</v>
       </c>
       <c r="K32" s="2" t="n"/>
       <c r="L32" s="2" t="n"/>
@@ -3596,7 +3589,7 @@
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t>The changes in mne/viz/_figure.py adjust how epochs are indexed and how bad-epoch highlighting colors are mapped during scrolling/drawing: (1) compute sampling_period from inst.times and use it to subtract one sample before searchsorted for t_start to avoid boundary-time precision misalignment; (2) fix a bug where the horizontal scroll boundary patch width incorrectly used boundary_times[:2] rather than boundary_times[ix:ix+2]; (3) change visible bad-epoch mapping from values to indices (visible_bad_epoch_ix) so the override of bad-epoch colors applies to the correct epoch columns after recomputation during scroll/redraw.</t>
+          <t>The patch changes MSM allocation/deallocation lifecycle in src/KSPACE/msm.cpp, especially adding deallocate() before reallocation in setup(), deallocating levels before rebuilding them in set_grid_global(), and fixing pointer/null handling in deallocate()/allocate_levels(), which directly targets a memory/state corruption path consistent with the MSM accuracy regression report.</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3607,52 +3600,52 @@
       <c r="R32" s="3" t="inlineStr"/>
       <c r="S32" s="3" t="inlineStr">
         <is>
-          <t>By correcting boundary-time indexing precision and using correct epoch index mapping when drawing, the PR addresses the reported scroll/redraw mismatch where selection and dropped/highlighted epochs become inconsistent.</t>
+          <t>The PR modifies the MSM code path responsible for grid allocation and teardown, plausibly fixing the state corruption causing the force accuracy regression.</t>
         </is>
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t>Neuroscience</t>
+          <t>Materials Science</t>
         </is>
       </c>
       <c r="U32" s="3" t="inlineStr">
         <is>
-          <t>swe_dominant</t>
+          <t>joint</t>
         </is>
       </c>
       <c r="V32" s="3" t="inlineStr">
         <is>
-          <t>easy</t>
+          <t>hard</t>
         </is>
       </c>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>hard</t>
         </is>
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t>insufficient</t>
+          <t>sufficient</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>nilearn/nilearn</t>
+          <t>lammps/lammps</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>2705</v>
+        <v>2009</v>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>Possible identical design matrix columns with generate_fake_fmri_data_and_design</t>
+          <t>[BUG] Replicate not copying extra bonds/angles/etc</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/nilearn/nilearn/issues/2705</t>
+          <t>https://github.com/lammps/lammps/issues/2009</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -3662,18 +3655,26 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G33" s="3" t="inlineStr"/>
-      <c r="H33" s="3" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>https://user-images.githubusercontent.com/48093480/78852484-05691800-7a4f-11ea-9479-7c09f7c8efcd.JPG</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/nilearn/nilearn/pull/2706</t>
+          <t>https://github.com/lammps/lammps/pull/2010</t>
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>2706</v>
+        <v>2010</v>
       </c>
       <c r="K33" s="2" t="n"/>
       <c r="L33" s="2" t="n"/>
@@ -3690,7 +3691,7 @@
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t>The patch changes generate_fake_fmri_data_and_design to sample column labels with replace=False instead of the previous default sampling with replacement, preventing duplicate column names (e.g., 'a-a') that can make contrast computations degenerate.</t>
+          <t>The PR changes src/KSPACE/pair_lj_long_coul_long.cpp and src/KSPACE/pair_buck_long_coul_long.cpp, and the implementation note explicitly says the per-type-pair cutoff may not be written when LJ processing is set to long so that only the global cutoff is used, otherwise garbage data is written; this matches the reported wrong write_coeff output for lj/long/coul/long and lj/long/tip4p/long.</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -3701,78 +3702,73 @@
       <c r="R33" s="3" t="inlineStr"/>
       <c r="S33" s="3" t="inlineStr">
         <is>
-          <t>Sampling without replacement directly removes the mechanism that produced identically named design-matrix columns, addressing the random contrast failure.</t>
+          <t>The patch directly targets the affected long-range pair-style write_data/write_coeff path and corrects the per-type-pair cutoff handling that caused the wrong coefficients.</t>
         </is>
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t>Neuroscience</t>
+          <t>Materials Science</t>
         </is>
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t>swe_dominant</t>
+          <t>joint</t>
         </is>
       </c>
       <c r="V33" s="3" t="inlineStr">
         <is>
-          <t>easy</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t>easy</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="X33" s="3" t="inlineStr">
         <is>
-          <t>insufficient</t>
+          <t>sufficient</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>nilearn/nilearn</t>
+          <t>lammps/lammps</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>2430</v>
+        <v>1935</v>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>Incorrect colorbar with thresholded statmap</t>
+          <t>[BUG] Out of range atoms - cannot compute PPPM with triclinic box and user-intel</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/nilearn/nilearn/issues/2430</t>
+          <t>https://github.com/lammps/lammps/issues/1935</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G34" s="3" t="inlineStr">
-        <is>
-          <t>https://user-images.githubusercontent.com/54182/80816934-714a2680-8b9e-11ea-8e43-b240ead33bd5.png
-https://user-images.githubusercontent.com/54182/80817874-39dc7980-8ba0-11ea-82fd-7979f88d429f.png</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr"/>
       <c r="H34" s="3" t="inlineStr"/>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/nilearn/nilearn/pull/2431</t>
+          <t>https://github.com/lammps/lammps/pull/1928</t>
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>2431</v>
+        <v>1928</v>
       </c>
       <c r="K34" s="2" t="n"/>
       <c r="L34" s="2" t="n"/>
@@ -3789,7 +3785,7 @@
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t>The PR modifies nilearn/plotting/img_plotting.py _crop_colorbar to handle Matplotlib &gt;=3.2.0 by setting the colorbar axis limits with the un-normalized cbar_vmin/cbar_vmax and recomputing the outline via cbar._mesh()/cbar._outline, while keeping the previous cbar.norm-based logic for older Matplotlib versions; this directly addresses the reported mechanism where colorbars were incorrectly scaled between 0 and 1 after a Matplotlib API change.</t>
+          <t>The patch changes src/USER-INTEL/pppm_intel.cpp to route triclinic-cell grid operations through the plain PPPM code path instead of the USER-INTEL coordinate-buffer path, which matches the reported out-of-range atom failure in pppm/intel with triclinic boxes.</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -3800,32 +3796,32 @@
       <c r="R34" s="3" t="inlineStr"/>
       <c r="S34" s="3" t="inlineStr">
         <is>
-          <t>Because the fix changes the colorbar cropping logic to use the correct axis scaling depending on the Matplotlib version, it plausibly restores the intended correspondence between thresholded statmap values and the colorbar range.</t>
+          <t>The implementation directly targets the reported triclinic/pppm-intel failure mode at the affected code path and plausibly restores correct behavior while preserving orthogonal-cell behavior.</t>
         </is>
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t>Neuroscience</t>
+          <t>Materials Science</t>
         </is>
       </c>
       <c r="U34" s="3" t="inlineStr">
         <is>
-          <t>swe_dominant</t>
+          <t>joint</t>
         </is>
       </c>
       <c r="V34" s="3" t="inlineStr">
         <is>
-          <t>easy</t>
+          <t>hard</t>
         </is>
       </c>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>hard</t>
         </is>
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t>insufficient</t>
+          <t>sufficient</t>
         </is>
       </c>
     </row>
@@ -3836,16 +3832,16 @@
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>2175</v>
+        <v>1753</v>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>[BUG] Pressure offset in NPT run with GPU accelerated TIP4P</t>
+          <t>[BUG] special bonds are not treated correctly when pair_style hybrid has two lj/cut/coul/dsf</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/lammps/lammps/issues/2175</t>
+          <t>https://github.com/lammps/lammps/issues/1753</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -3855,22 +3851,22 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G35" s="3" t="inlineStr">
-        <is>
-          <t>https://user-images.githubusercontent.com/19315755/85327891-95323600-b484-11ea-8777-84fd2552c1f1.png</t>
-        </is>
-      </c>
-      <c r="H35" s="3" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr"/>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/lammps/lammps/pull/2187</t>
+          <t>https://github.com/lammps/lammps/pull/1759</t>
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>2187</v>
+        <v>1759</v>
       </c>
       <c r="K35" s="2" t="n"/>
       <c r="L35" s="2" t="n"/>
@@ -3887,7 +3883,7 @@
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t>The fix changes GPU TIP4P virial accumulation logic in the exact code path reported by the issue (`lib/gpu/lal_lj_tip4p_long.cu`) and updates the GPU pair wrapper to initialize energy/virial bookkeeping correctly; the PR body explicitly states it fixes incorrect virial accumulation for `eflag == 0, vflag == 1`, matching the reported pressure offset in NPT GPU TIP4P runs.</t>
+          <t>The patch changes Neighbor::init() so the special-bonds exclusion logic now explicitly detects kspace-like substyles inside pair_style hybrid (including multiple matching coul/wolf, coul/dsf, or thole substyles) and keeps special_flag[1..3]=2, which matches the reported failure mode.</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -3898,7 +3894,7 @@
       <c r="R35" s="3" t="inlineStr"/>
       <c r="S35" s="3" t="inlineStr">
         <is>
-          <t>The change directly addresses the GPU TIP4P virial/pressure computation path that caused the reported pressure offset, so it is a relevant direct fix.</t>
+          <t>This is a domain-specific numerical correctness bug in LAMMPS special-bonds handling, and the code change directly targets the reported hybrid sub-style matching failure.</t>
         </is>
       </c>
       <c r="T35" s="3" t="inlineStr">
@@ -3918,7 +3914,7 @@
       </c>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t>hard</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="X35" s="3" t="inlineStr">
@@ -3934,16 +3930,16 @@
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>2178</v>
+        <v>1702</v>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>[BUG] Accuracy regression in MSM</t>
+          <t>[BUG]  Gay-Berne pair style do not conserve energy with negative exponents</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/lammps/lammps/issues/2178</t>
+          <t>https://github.com/lammps/lammps/issues/1702</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -3964,11 +3960,11 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/lammps/lammps/pull/2181</t>
+          <t>https://github.com/lammps/lammps/pull/1746</t>
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>2181</v>
+        <v>1746</v>
       </c>
       <c r="K36" s="2" t="n"/>
       <c r="L36" s="2" t="n"/>
@@ -3985,7 +3981,7 @@
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t>The patch changes MSM allocation/deallocation lifecycle in src/KSPACE/msm.cpp, especially adding deallocate() before reallocation in setup(), deallocating levels before rebuilding them in set_grid_global(), and fixing pointer/null handling in deallocate()/allocate_levels(), which directly targets a memory/state corruption path consistent with the MSM accuracy regression report.</t>
+          <t>The patch changes Gay-Berne force/torque derivative scaling in the active pair style implementations (ASPHERE, GPU, and USER-INTEL) and updates the torque derivation documentation, matching the reported energy drift mechanism in pair_style gayberne with non-unit mu.</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -3996,7 +3992,7 @@
       <c r="R36" s="3" t="inlineStr"/>
       <c r="S36" s="3" t="inlineStr">
         <is>
-          <t>The PR modifies the MSM code path responsible for grid allocation and teardown, plausibly fixing the state corruption causing the force accuracy regression.</t>
+          <t>The PR directly modifies the Gay-Berne derivative terms at the reported code path across implementations, plausibly correcting the torque/force calculation responsible for the energy drift.</t>
         </is>
       </c>
       <c r="T36" s="3" t="inlineStr">
@@ -4006,7 +4002,7 @@
       </c>
       <c r="U36" s="3" t="inlineStr">
         <is>
-          <t>joint</t>
+          <t>science_dominant</t>
         </is>
       </c>
       <c r="V36" s="3" t="inlineStr">
@@ -4016,7 +4012,7 @@
       </c>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t>hard</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="X36" s="3" t="inlineStr">
@@ -4032,16 +4028,16 @@
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>2009</v>
+        <v>1695</v>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>[BUG] Replicate not copying extra bonds/angles/etc</t>
+          <t>[BUG] fix pour: particles overlapping at z periodic boundary</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/lammps/lammps/issues/2009</t>
+          <t>https://github.com/lammps/lammps/issues/1695</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -4051,14 +4047,10 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G37" s="3" t="inlineStr">
-        <is>
-          <t>https://user-images.githubusercontent.com/48093480/78852484-05691800-7a4f-11ea-9479-7c09f7c8efcd.JPG</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr"/>
       <c r="H37" s="3" t="inlineStr">
         <is>
           <t>bug</t>
@@ -4066,11 +4058,11 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/lammps/lammps/pull/2010</t>
+          <t>https://github.com/lammps/lammps/pull/1750</t>
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>2010</v>
+        <v>1750</v>
       </c>
       <c r="K37" s="2" t="n"/>
       <c r="L37" s="2" t="n"/>
@@ -4087,7 +4079,7 @@
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t>The PR changes src/KSPACE/pair_lj_long_coul_long.cpp and src/KSPACE/pair_buck_long_coul_long.cpp, and the implementation note explicitly says the per-type-pair cutoff may not be written when LJ processing is set to long so that only the global cutoff is used, otherwise garbage data is written; this matches the reported wrong write_coeff output for lj/long/coul/long and lj/long/tip4p/long.</t>
+          <t>The patch changes fix_pour's boundary classification logic in the affected outside() path so that periodic z-boundary handling is corrected from an OR-like condition to the intended combined check, matching the reported overlap mechanism.</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4098,7 +4090,7 @@
       <c r="R37" s="3" t="inlineStr"/>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t>The patch directly targets the affected long-range pair-style write_data/write_coeff path and corrects the per-type-pair cutoff handling that caused the wrong coefficients.</t>
+          <t>The modified outside() logic directly addresses the reported z-periodic overlap bug in fix_pour by fixing the periodic-boundary inclusion test.</t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
@@ -4108,22 +4100,22 @@
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t>joint</t>
+          <t>swe_dominant</t>
         </is>
       </c>
       <c r="V37" s="3" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>easy</t>
         </is>
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>easy</t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t>sufficient</t>
+          <t>insufficient</t>
         </is>
       </c>
     </row>
@@ -4134,21 +4126,21 @@
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>1935</v>
+        <v>869</v>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>[BUG] Out of range atoms - cannot compute PPPM with triclinic box and user-intel</t>
+          <t>Unexpected out of range atoms error with pppm/tip4p and triclinic boxes</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/lammps/lammps/issues/1935</t>
+          <t>https://github.com/lammps/lammps/issues/869</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1,2</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -4157,14 +4149,19 @@
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr"/>
-      <c r="H38" s="3" t="inlineStr"/>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>bug
+kspace_package</t>
+        </is>
+      </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/lammps/lammps/pull/1928</t>
+          <t>https://github.com/lammps/lammps/pull/1719</t>
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>1928</v>
+        <v>1719</v>
       </c>
       <c r="K38" s="2" t="n"/>
       <c r="L38" s="2" t="n"/>
@@ -4181,7 +4178,7 @@
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t>The patch changes src/USER-INTEL/pppm_intel.cpp to route triclinic-cell grid operations through the plain PPPM code path instead of the USER-INTEL coordinate-buffer path, which matches the reported out-of-range atom failure in pppm/intel with triclinic boxes.</t>
+          <t>The patch changes the PPPM/TIP4P triclinic M-site construction in src/KSPACE/pppm_tip4p.cpp and src/USER-OMP/pppm_tip4p_omp.cpp so local atoms are converted with lamda2x while ghost atoms are not, which matches the reported failure mode for triclinic boxes; it also enables triclinic support in the OMP kspace path, aligning with the issue and closing PR title.</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4192,7 +4189,7 @@
       <c r="R38" s="3" t="inlineStr"/>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t>The implementation directly targets the reported triclinic/pppm-intel failure mode at the affected code path and plausibly restores correct behavior while preserving orthogonal-cell behavior.</t>
+          <t>The PR directly fixes the PPPM/TIP4P triclinic coordinate handling at the implicated code path, plausibly addressing both the wrong energies and the out-of-range atoms crash.</t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
@@ -4228,16 +4225,16 @@
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>1753</v>
+        <v>726</v>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>[BUG] special bonds are not treated correctly when pair_style hybrid has two lj/cut/coul/dsf</t>
+          <t>REBO parameters</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/lammps/lammps/issues/1753</t>
+          <t>https://github.com/lammps/lammps/issues/726</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -4251,18 +4248,14 @@
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr"/>
-      <c r="H39" s="3" t="inlineStr">
-        <is>
-          <t>bug</t>
-        </is>
-      </c>
+      <c r="H39" s="3" t="inlineStr"/>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/lammps/lammps/pull/1759</t>
+          <t>https://github.com/lammps/lammps/pull/1452</t>
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>1759</v>
+        <v>1452</v>
       </c>
       <c r="K39" s="2" t="n"/>
       <c r="L39" s="2" t="n"/>
@@ -4279,7 +4272,7 @@
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t>The patch changes Neighbor::init() so the special-bonds exclusion logic now explicitly detects kspace-like substyles inside pair_style hybrid (including multiple matching coul/wolf, coul/dsf, or thole substyles) and keeps special_flag[1..3]=2, which matches the reported failure mode.</t>
+          <t>The patch introduces a dedicated CH.rebo potential file and updates pair_rebo and related examples/docs to use it, while preserving CH.airebo for AIREBO, matching the reported need to change REBO parameters independently of AIREBO.</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4290,7 +4283,7 @@
       <c r="R39" s="3" t="inlineStr"/>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t>This is a domain-specific numerical correctness bug in LAMMPS special-bonds handling, and the code change directly targets the reported hybrid sub-style matching failure.</t>
+          <t>The change directly addresses the reported scientific correctness bug by separating REBO from AIREBO parameterization and wiring REBO to its own parameter file.</t>
         </is>
       </c>
       <c r="T39" s="3" t="inlineStr">
@@ -4300,7 +4293,7 @@
       </c>
       <c r="U39" s="3" t="inlineStr">
         <is>
-          <t>joint</t>
+          <t>science_dominant</t>
         </is>
       </c>
       <c r="V39" s="3" t="inlineStr">
@@ -4326,16 +4319,16 @@
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>1702</v>
+        <v>1385</v>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>[BUG]  Gay-Berne pair style do not conserve energy with negative exponents</t>
+          <t>[BUG]  MPI error when using fix balance rcb with hybrid ellipsoid particles and periodic boundary conditions</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/lammps/lammps/issues/1702</t>
+          <t>https://github.com/lammps/lammps/issues/1385</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -4351,16 +4344,17 @@
       <c r="G40" s="3" t="inlineStr"/>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>bug</t>
+          <t>bug
+communication_feature</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/lammps/lammps/pull/1746</t>
+          <t>https://github.com/lammps/lammps/pull/1388</t>
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>1746</v>
+        <v>1388</v>
       </c>
       <c r="K40" s="2" t="n"/>
       <c r="L40" s="2" t="n"/>
@@ -4377,7 +4371,7 @@
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t>The patch changes Gay-Berne force/torque derivative scaling in the active pair style implementations (ASPHERE, GPU, and USER-INTEL) and updates the torque derivation documentation, matching the reported energy drift mechanism in pair_style gayberne with non-unit mu.</t>
+          <t>The patch changes tiled communication to avoid incorrect self-send handling in CommTiled::forward_comm for the sendother path and fixes fix_balance output timing around rebalance, which directly targets the reported deadlock/mpi error mechanism with periodic boundaries and RCB balance.</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4388,7 +4382,7 @@
       <c r="R40" s="3" t="inlineStr"/>
       <c r="S40" s="3" t="inlineStr">
         <is>
-          <t>The PR directly modifies the Gay-Berne derivative terms at the reported code path across implementations, plausibly correcting the torque/force calculation responsible for the energy drift.</t>
+          <t>The code change is localized to the communication path implicated by the bug and plausibly removes the MPI hang/crash cause reported for tiled communications under periodic boundaries.</t>
         </is>
       </c>
       <c r="T40" s="3" t="inlineStr">
@@ -4398,7 +4392,7 @@
       </c>
       <c r="U40" s="3" t="inlineStr">
         <is>
-          <t>science_dominant</t>
+          <t>joint</t>
         </is>
       </c>
       <c r="V40" s="3" t="inlineStr">
@@ -4408,7 +4402,7 @@
       </c>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>hard</t>
         </is>
       </c>
       <c r="X40" s="3" t="inlineStr">
@@ -4424,16 +4418,16 @@
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>1695</v>
+        <v>1378</v>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>[BUG] fix pour: particles overlapping at z periodic boundary</t>
+          <t>[BUG] Possible problem in dump_modify pbc</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/lammps/lammps/issues/1695</t>
+          <t>https://github.com/lammps/lammps/issues/1378</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -4454,11 +4448,11 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/lammps/lammps/pull/1750</t>
+          <t>https://github.com/lammps/lammps/pull/1374</t>
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>1750</v>
+        <v>1374</v>
       </c>
       <c r="K41" s="2" t="n"/>
       <c r="L41" s="2" t="n"/>
@@ -4475,7 +4469,7 @@
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t>The patch changes fix_pour's boundary classification logic in the affected outside() path so that periodic z-boundary handling is corrected from an OR-like condition to the intended combined check, matching the reported overlap mechanism.</t>
+          <t>The patch explicitly adds a bugfix for `dump_modify pbc yes` with triclinic cells and changes `src/dump.cpp`, matching the reported wrong wrapping behavior in tilted boxes.</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -4486,7 +4480,7 @@
       <c r="R41" s="3" t="inlineStr"/>
       <c r="S41" s="3" t="inlineStr">
         <is>
-          <t>The modified outside() logic directly addresses the reported z-periodic overlap bug in fix_pour by fixing the periodic-boundary inclusion test.</t>
+          <t>The PR directly states and touches the dump code path implicated by the triclinic `dump_modify pbc` wrapping bug, so it plausibly fixes the reported behavior.</t>
         </is>
       </c>
       <c r="T41" s="3" t="inlineStr">
@@ -4496,22 +4490,22 @@
       </c>
       <c r="U41" s="3" t="inlineStr">
         <is>
-          <t>swe_dominant</t>
+          <t>joint</t>
         </is>
       </c>
       <c r="V41" s="3" t="inlineStr">
         <is>
-          <t>easy</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t>easy</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t>insufficient</t>
+          <t>sufficient</t>
         </is>
       </c>
     </row>
@@ -4522,16 +4516,16 @@
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>869</v>
+        <v>1236</v>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>Unexpected out of range atoms error with pppm/tip4p and triclinic boxes</t>
+          <t>segmentation fault with stress/mop/profile and atom_style sphere</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/lammps/lammps/issues/869</t>
+          <t>https://github.com/lammps/lammps/issues/1236</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -4547,17 +4541,16 @@
       <c r="G42" s="3" t="inlineStr"/>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>bug
-kspace_package</t>
+          <t>bug</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/lammps/lammps/pull/1719</t>
+          <t>https://github.com/lammps/lammps/pull/1237</t>
         </is>
       </c>
       <c r="J42" s="2" t="n">
-        <v>1719</v>
+        <v>1237</v>
       </c>
       <c r="K42" s="2" t="n"/>
       <c r="L42" s="2" t="n"/>
@@ -4574,7 +4567,7 @@
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t>The patch changes the PPPM/TIP4P triclinic M-site construction in src/KSPACE/pppm_tip4p.cpp and src/USER-OMP/pppm_tip4p_omp.cpp so local atoms are converted with lamda2x while ghost atoms are not, which matches the reported failure mode for triclinic boxes; it also enables triclinic support in the OMP kspace path, aligning with the issue and closing PR title.</t>
+          <t>Patch adds support for atom-&gt;rmass in compute_stress_mop and compute_stress_mop_profile, replacing per-type mass-only calculations in the kinetic/crossing-velocity path that caused crashes for atom_style sphere/per-atom masses.</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -4585,7 +4578,7 @@
       <c r="R42" s="3" t="inlineStr"/>
       <c r="S42" s="3" t="inlineStr">
         <is>
-          <t>The PR directly fixes the PPPM/TIP4P triclinic coordinate handling at the implicated code path, plausibly addressing both the wrong energies and the out-of-range atoms crash.</t>
+          <t>The change directly addresses the reported segmentation fault mechanism by handling per-atom masses in the affected scientific compute routines.</t>
         </is>
       </c>
       <c r="T42" s="3" t="inlineStr">
@@ -4600,12 +4593,12 @@
       </c>
       <c r="V42" s="3" t="inlineStr">
         <is>
-          <t>hard</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t>hard</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="X42" s="3" t="inlineStr">
@@ -4617,20 +4610,20 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>lammps/lammps</t>
+          <t>pyscf/pyscf</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>726</v>
+        <v>1028</v>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>REBO parameters</t>
+          <t>feature request: spherical averaged dft</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/lammps/lammps/issues/726</t>
+          <t>https://github.com/pyscf/pyscf/issues/1028</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -4647,11 +4640,11 @@
       <c r="H43" s="3" t="inlineStr"/>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/lammps/lammps/pull/1452</t>
+          <t>https://github.com/pyscf/pyscf/pull/1143</t>
         </is>
       </c>
       <c r="J43" s="2" t="n">
-        <v>1452</v>
+        <v>1143</v>
       </c>
       <c r="K43" s="2" t="n"/>
       <c r="L43" s="2" t="n"/>
@@ -4668,7 +4661,7 @@
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t>The patch introduces a dedicated CH.rebo potential file and updates pair_rebo and related examples/docs to use it, while preserving CH.airebo for AIREBO, matching the reported need to change REBO parameters independently of AIREBO.</t>
+          <t>The reported issue asks for spherically averaged atomic DFT analogous to existing spherically averaged HF. The PR adds a new module pyscf/scf/atom_ks.py and modifies pyscf/scf/atom_hf.py to include additional logic, plus adds atomic configuration data (NRSRHFS_CONFIGURATION) for exchange-only LDA/HFS use in atomic SAD calculations. This directly implements the missing spherically averaged Kohn-Sham/DFT atomic capability in the same location/pattern as the existing SAD HF machinery (atom_hf).</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -4679,12 +4672,12 @@
       <c r="R43" s="3" t="inlineStr"/>
       <c r="S43" s="3" t="inlineStr">
         <is>
-          <t>The change directly addresses the reported scientific correctness bug by separating REBO from AIREBO parameterization and wiring REBO to its own parameter file.</t>
+          <t>Adding pyscf/scf/atom_ks.py together with SAD DFT-specific atomic configurations and wiring indicates the PR implements the requested spherically averaged atomic DFT functionality rather than merely suggesting code changes or addressing unrelated aspects.</t>
         </is>
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t>Materials Science</t>
+          <t>Chemistry</t>
         </is>
       </c>
       <c r="U43" s="3" t="inlineStr">
@@ -4711,20 +4704,20 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>lammps/lammps</t>
+          <t>pyscf/pyscf</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>1385</v>
+        <v>1162</v>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>[BUG]  MPI error when using fix balance rcb with hybrid ellipsoid particles and periodic boundary conditions</t>
+          <t>Huckel guess fails if mol.cart = True</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/lammps/lammps/issues/1385</t>
+          <t>https://github.com/pyscf/pyscf/issues/1162</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -4738,19 +4731,14 @@
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr"/>
-      <c r="H44" s="3" t="inlineStr">
-        <is>
-          <t>bug
-communication_feature</t>
-        </is>
-      </c>
+      <c r="H44" s="3" t="inlineStr"/>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/lammps/lammps/pull/1388</t>
+          <t>https://github.com/pyscf/pyscf/pull/1164</t>
         </is>
       </c>
       <c r="J44" s="2" t="n">
-        <v>1388</v>
+        <v>1164</v>
       </c>
       <c r="K44" s="2" t="n"/>
       <c r="L44" s="2" t="n"/>
@@ -4767,7 +4755,7 @@
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
-          <t>The patch changes tiled communication to avoid incorrect self-send handling in CommTiled::forward_comm for the sendother path and fixes fix_balance output timing around rebalance, which directly targets the reported deadlock/mpi error mechanism with periodic boundaries and RCB balance.</t>
+          <t>The reported failure arises in `hf.py` during `_init_guess_huckel_orbitals` when assigning atomic Huckel guess coefficients into an AO block; the patch adds a cartesian-to-spherical mapping when `mol.cart=True` and transforms `at_c` columns via `cart2sph` before assignment, preventing the shape mismatch (`(14)` vs `(15)`) by making the coefficient representation consistent with the target AO basis block.</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -4778,12 +4766,12 @@
       <c r="R44" s="3" t="inlineStr"/>
       <c r="S44" s="3" t="inlineStr">
         <is>
-          <t>The code change is localized to the communication path implicated by the bug and plausibly removes the MPI hang/crash cause reported for tiled communications under periodic boundaries.</t>
+          <t>The fix directly addresses the mechanism of the broadcasting error by converting the Huckel atomic orbital coefficients into the same (cartesian) AO representation used for `orb_C` when `mol.cart=True`.</t>
         </is>
       </c>
       <c r="T44" s="3" t="inlineStr">
         <is>
-          <t>Materials Science</t>
+          <t>Chemistry</t>
         </is>
       </c>
       <c r="U44" s="3" t="inlineStr">
@@ -4793,12 +4781,12 @@
       </c>
       <c r="V44" s="3" t="inlineStr">
         <is>
-          <t>hard</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="W44" s="3" t="inlineStr">
         <is>
-          <t>hard</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="X44" s="3" t="inlineStr">
@@ -4810,20 +4798,20 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>lammps/lammps</t>
+          <t>pyscf/pyscf</t>
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>1378</v>
+        <v>793</v>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>[BUG] Possible problem in dump_modify pbc</t>
+          <t>TDDFT with range-separated functionals</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/lammps/lammps/issues/1378</t>
+          <t>https://github.com/pyscf/pyscf/issues/793</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -4837,18 +4825,14 @@
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr"/>
-      <c r="H45" s="3" t="inlineStr">
-        <is>
-          <t>bug</t>
-        </is>
-      </c>
+      <c r="H45" s="3" t="inlineStr"/>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/lammps/lammps/pull/1374</t>
+          <t>https://github.com/pyscf/pyscf/pull/794</t>
         </is>
       </c>
       <c r="J45" s="2" t="n">
-        <v>1374</v>
+        <v>794</v>
       </c>
       <c r="K45" s="2" t="n"/>
       <c r="L45" s="2" t="n"/>
@@ -4865,7 +4849,7 @@
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t>The patch explicitly adds a bugfix for `dump_modify pbc yes` with triclinic cells and changes `src/dump.cpp`, matching the reported wrong wrapping behavior in tilted boxes.</t>
+          <t>The PR modifies `pyscf/dft/libxc.py:is_hybrid_xc` so that range-separated functionals (via `rsh_coeff(xc_code)`) are treated as hybrid/so-called hybrid-capable. This directly aligns with the reported mechanism: TDDFT selects the wrong driver when the functional is passed via the LibXC keyword form `hyb_gga_xc_cam_b3lyp`, and the change makes PySCF classify such CAM-B3LYP as hybrid as well.</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -4876,17 +4860,17 @@
       <c r="R45" s="3" t="inlineStr"/>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t>The PR directly states and touches the dump code path implicated by the triclinic `dump_modify pbc` wrapping bug, so it plausibly fixes the reported behavior.</t>
+          <t>The code change adds explicit range-separated detection to the hybrid-classification logic, which plausibly fixes the TDDFT driver mis-selection that occurred for CAM-B3LYP passed as a LibXC keyword.</t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t>Materials Science</t>
+          <t>Chemistry</t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t>joint</t>
+          <t>science_dominant</t>
         </is>
       </c>
       <c r="V45" s="3" t="inlineStr">
@@ -4896,7 +4880,7 @@
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>easy</t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
@@ -4908,25 +4892,25 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>lammps/lammps</t>
+          <t>psi4/psi4</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
-        <v>1236</v>
+        <v>2452</v>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>segmentation fault with stress/mop/profile and atom_style sphere</t>
+          <t>Typo in left eigenvector beta in scf_response.py tdscf_excitations</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/lammps/lammps/issues/1236</t>
+          <t>https://github.com/psi4/psi4/issues/2452</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -4935,18 +4919,14 @@
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr"/>
-      <c r="H46" s="3" t="inlineStr">
-        <is>
-          <t>bug</t>
-        </is>
-      </c>
+      <c r="H46" s="3" t="inlineStr"/>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/lammps/lammps/pull/1237</t>
+          <t>https://github.com/psi4/psi4/pull/2453</t>
         </is>
       </c>
       <c r="J46" s="2" t="n">
-        <v>1237</v>
+        <v>2453</v>
       </c>
       <c r="K46" s="2" t="n"/>
       <c r="L46" s="2" t="n"/>
@@ -4963,7 +4943,7 @@
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t>Patch adds support for atom-&gt;rmass in compute_stress_mop and compute_stress_mop_profile, replacing per-type mass-only calculations in the kinetic/crossing-velocity path that caused crashes for atom_style sphere/per-atom masses.</t>
+          <t>The PR patch changes the export variable for TD-LEFT EIGENVECTOR ALPHA to TD-LEFT EIGENVECTOR BETA and removes the overwriting/incorrect assignment of the alpha value with beta, aligning left eigenvector labels with the underlying L_eigvec indices.</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -4974,52 +4954,52 @@
       <c r="R46" s="3" t="inlineStr"/>
       <c r="S46" s="3" t="inlineStr">
         <is>
-          <t>The change directly addresses the reported segmentation fault mechanism by handling per-atom masses in the affected scientific compute routines.</t>
+          <t>The diff directly updates the specific variable name so that the stored left eigenvector uses the intended beta slot instead of overwriting the alpha slot.</t>
         </is>
       </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
-          <t>Materials Science</t>
+          <t>Chemistry</t>
         </is>
       </c>
       <c r="U46" s="3" t="inlineStr">
         <is>
-          <t>joint</t>
+          <t>swe_dominant</t>
         </is>
       </c>
       <c r="V46" s="3" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>easy</t>
         </is>
       </c>
       <c r="W46" s="3" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>easy</t>
         </is>
       </c>
       <c r="X46" s="3" t="inlineStr">
         <is>
-          <t>sufficient</t>
+          <t>insufficient</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>pyscf/pyscf</t>
+          <t>obspy/obspy</t>
         </is>
       </c>
       <c r="B47" s="2" t="n">
-        <v>1028</v>
+        <v>870</v>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>feature request: spherical averaged dft</t>
+          <t>Array analysis matplotlib date conversion bug</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pyscf/pyscf/issues/1028</t>
+          <t>https://github.com/obspy/obspy/issues/870</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -5033,14 +5013,19 @@
         </is>
       </c>
       <c r="G47" s="3" t="inlineStr"/>
-      <c r="H47" s="3" t="inlineStr"/>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>bug
+.signal</t>
+        </is>
+      </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pyscf/pyscf/pull/1143</t>
+          <t>https://github.com/obspy/obspy/pull/956</t>
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>1143</v>
+        <v>956</v>
       </c>
       <c r="K47" s="2" t="n"/>
       <c r="L47" s="2" t="n"/>
@@ -5057,7 +5042,7 @@
       </c>
       <c r="P47" s="3" t="inlineStr">
         <is>
-          <t>The reported issue asks for spherically averaged atomic DFT analogous to existing spherically averaged HF. The PR adds a new module pyscf/scf/atom_ks.py and modifies pyscf/scf/atom_hf.py to include additional logic, plus adds atomic configuration data (NRSRHFS_CONFIGURATION) for exchange-only LDA/HFS use in atomic SAD calculations. This directly implements the missing spherically averaged Kohn-Sham/DFT atomic capability in the same location/pattern as the existing SAD HF machinery (atom_hf).</t>
+          <t>The code change adjusts the mlabday conversion constant from adding 719162 hours between 1970 and 0001 to adding 719163 days between 1970 and 0001 (+1 epoch offset), aligning with the reported Rata Die epoch starting at 1 instead of 0.</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5068,52 +5053,52 @@
       <c r="R47" s="3" t="inlineStr"/>
       <c r="S47" s="3" t="inlineStr">
         <is>
-          <t>Adding pyscf/scf/atom_ks.py together with SAD DFT-specific atomic configurations and wiring indicates the PR implements the requested spherically averaged atomic DFT functionality rather than merely suggesting code changes or addressing unrelated aspects.</t>
+          <t>The implementation directly applies the requested +1 correction to the mlabday numeric conversion used by array_processing.</t>
         </is>
       </c>
       <c r="T47" s="3" t="inlineStr">
         <is>
-          <t>Chemistry</t>
+          <t>Earth Science</t>
         </is>
       </c>
       <c r="U47" s="3" t="inlineStr">
         <is>
-          <t>science_dominant</t>
+          <t>swe_dominant</t>
         </is>
       </c>
       <c r="V47" s="3" t="inlineStr">
         <is>
-          <t>hard</t>
+          <t>easy</t>
         </is>
       </c>
       <c r="W47" s="3" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>easy</t>
         </is>
       </c>
       <c r="X47" s="3" t="inlineStr">
         <is>
-          <t>sufficient</t>
+          <t>insufficient</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>pyscf/pyscf</t>
+          <t>astropy/astropy</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
-        <v>1162</v>
+        <v>6391</v>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>Huckel guess fails if mol.cart = True</t>
+          <t>Wrong Earth radius</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pyscf/pyscf/issues/1162</t>
+          <t>https://github.com/astropy/astropy/issues/6391</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -5123,18 +5108,27 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G48" s="3" t="inlineStr"/>
-      <c r="H48" s="3" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr">
+        <is>
+          <t>https://user-images.githubusercontent.com/316517/28540393-7f1ce650-70b5-11e7-85f5-e8901b7ae6ec.png</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>Bug
+constants</t>
+        </is>
+      </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pyscf/pyscf/pull/1164</t>
+          <t>https://github.com/astropy/astropy/pull/6400</t>
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>1164</v>
+        <v>6400</v>
       </c>
       <c r="K48" s="2" t="n"/>
       <c r="L48" s="2" t="n"/>
@@ -5151,7 +5145,7 @@
       </c>
       <c r="P48" s="3" t="inlineStr">
         <is>
-          <t>The reported failure arises in `hf.py` during `_init_guess_huckel_orbitals` when assigning atomic Huckel guess coefficients into an AO block; the patch adds a cartesian-to-spherical mapping when `mol.cart=True` and transforms `at_c` columns via `cart2sph` before assignment, preventing the shape mismatch (`(14)` vs `(15)`) by making the coefficient representation consistent with the target AO basis block.</t>
+          <t>The PR changes updated the IAU2015 Earth equatorial radius constant value from 6.3568e6 to 6.3781e6 and synchronized the `earthRad` unit/registry mappings accordingly, matching IAU 2015 Resolution B3’s nominal equatorial radius (while the issue reports the polar value was mistakenly used).</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5162,27 +5156,27 @@
       <c r="R48" s="3" t="inlineStr"/>
       <c r="S48" s="3" t="inlineStr">
         <is>
-          <t>The fix directly addresses the mechanism of the broadcasting error by converting the Huckel atomic orbital coefficients into the same (cartesian) AO representation used for `orb_C` when `mol.cart=True`.</t>
+          <t>The reported wrong-radius bug is caused by using the polar nominal value where the equatorial nominal value is expected, and the PR directly corrects both the constant and unit equivalence values to 6.3781e6 m.</t>
         </is>
       </c>
       <c r="T48" s="3" t="inlineStr">
         <is>
-          <t>Chemistry</t>
+          <t>Astronomy</t>
         </is>
       </c>
       <c r="U48" s="3" t="inlineStr">
         <is>
-          <t>joint</t>
+          <t>science_dominant</t>
         </is>
       </c>
       <c r="V48" s="3" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>easy</t>
         </is>
       </c>
       <c r="W48" s="3" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>easy</t>
         </is>
       </c>
       <c r="X48" s="3" t="inlineStr">
@@ -5194,25 +5188,25 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>pyscf/pyscf</t>
+          <t>astropy/astropy</t>
         </is>
       </c>
       <c r="B49" s="2" t="n">
-        <v>793</v>
+        <v>16526</v>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>TDDFT with range-separated functionals</t>
+          <t>Missing prefixes for SI-Unit "Becquerel" in astropy.units</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pyscf/pyscf/issues/793</t>
+          <t>https://github.com/astropy/astropy/issues/16526</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -5221,14 +5215,19 @@
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr"/>
-      <c r="H49" s="3" t="inlineStr"/>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>units
+Bug</t>
+        </is>
+      </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pyscf/pyscf/pull/794</t>
+          <t>https://github.com/astropy/astropy/pull/16529</t>
         </is>
       </c>
       <c r="J49" s="2" t="n">
-        <v>794</v>
+        <v>16529</v>
       </c>
       <c r="K49" s="2" t="n"/>
       <c r="L49" s="2" t="n"/>
@@ -5245,7 +5244,7 @@
       </c>
       <c r="P49" s="3" t="inlineStr">
         <is>
-          <t>The PR modifies `pyscf/dft/libxc.py:is_hybrid_xc` so that range-separated functionals (via `rsh_coeff(xc_code)`) are treated as hybrid/so-called hybrid-capable. This directly aligns with the reported mechanism: TDDFT selects the wrong driver when the functional is passed via the LibXC keyword form `hyb_gga_xc_cam_b3lyp`, and the change makes PySCF classify such CAM-B3LYP as hybrid as well.</t>
+          <t>The PR changes `astropy/units/si.py` to set `prefixes=True` for the `Bq` (becquerel) and `Ci` (curie) unit definitions, changing them from `prefixes=False`; this directly enables SI-prefix generation (e.g., `u.MBq`) consistent with the issue’s expected behavior.</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5256,12 +5255,12 @@
       <c r="R49" s="3" t="inlineStr"/>
       <c r="S49" s="3" t="inlineStr">
         <is>
-          <t>The code change adds explicit range-separated detection to the hybrid-classification logic, which plausibly fixes the TDDFT driver mis-selection that occurred for CAM-B3LYP passed as a LibXC keyword.</t>
+          <t>Enabling `prefixes=True` in the unit definitions is the targeted mechanism to make prefixed units like `MBq` available, matching the reported missing-attribute bug.</t>
         </is>
       </c>
       <c r="T49" s="3" t="inlineStr">
         <is>
-          <t>Chemistry</t>
+          <t>Physics</t>
         </is>
       </c>
       <c r="U49" s="3" t="inlineStr">
@@ -5271,7 +5270,7 @@
       </c>
       <c r="V49" s="3" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>easy</t>
         </is>
       </c>
       <c r="W49" s="3" t="inlineStr">
@@ -5288,25 +5287,25 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>psi4/psi4</t>
+          <t>astropy/astropy</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
-        <v>3004</v>
+        <v>12518</v>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>Potential bug in getChebychevRoots</t>
+          <t>astropy.cosmology.utils.aszarr does not take Column object</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/psi4/psi4/issues/3004</t>
+          <t>https://github.com/astropy/astropy/issues/12518</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -5315,14 +5314,19 @@
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr"/>
-      <c r="H50" s="3" t="inlineStr"/>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>Bug
+cosmology</t>
+        </is>
+      </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/psi4/psi4/pull/3005</t>
+          <t>https://github.com/astropy/astropy/pull/12525</t>
         </is>
       </c>
       <c r="J50" s="2" t="n">
-        <v>3005</v>
+        <v>12525</v>
       </c>
       <c r="K50" s="2" t="n"/>
       <c r="L50" s="2" t="n"/>
@@ -5339,7 +5343,7 @@
       </c>
       <c r="P50" s="3" t="inlineStr">
         <is>
-          <t>The reported implementation used Chebyshev nodes for the second kind (x=cos(i*pi/(n+1))) but had weights inconsistent with that quadrature. The PR patch renames the routine to getChebychevRootsKind2 and explicitly updates the weights for Chebyshev quadrature of the second kind (A&amp;S/Treutler-Ahlrichs style), including the unit-form scaling via w=pi/(n+1)*sqrt(1-x^2) = pi/(n+1)*sin(i*pi/(n+1)). It also updates the scheme table entries (AHLRICHS/TREUTLER/BECKE) to use the corrected Kind2 function instead of the previous one.</t>
+          <t>The reported failure mode is that `aszarr` checks `hasattr(z, "unit")` and then calls `z.to_value(cu.redshift)`, which raises `AttributeError` for `astropy.table.Column` (Column has `unit` but no `to_value`). The closing PR modifies `astropy/cosmology/utils.py` so that when an object has `unit` (treated as Quantity/Column-like), it converts via an operation that works for both Quantity and Column: `(z &lt;&lt; cu.redshift).value` instead of `z.to_value(cu.redshift)`. The PR title/body explicitly states it fixes handling of `Column` objects for `astropy.cosmology.utils.aszarr`, and the code change targets the exact conversion path that previously called `to_value`.</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -5350,22 +5354,22 @@
       <c r="R50" s="3" t="inlineStr"/>
       <c r="S50" s="3" t="inlineStr">
         <is>
-          <t>The fix changes both the targeted weight formula and the use-sites to the correct Chebyshev quadrature of the second kind, plausibly resolving the node/weight mismatch described.</t>
+          <t>The change replaces the Quantity-only `.to_value(cu.redshift)` call with a conversion expression that supports `Column` objects that provide `unit` but not `.to_value`, thereby preventing the reported `AttributeError` and producing redshift values consistently.</t>
         </is>
       </c>
       <c r="T50" s="3" t="inlineStr">
         <is>
-          <t>Chemistry</t>
+          <t>Astronomy</t>
         </is>
       </c>
       <c r="U50" s="3" t="inlineStr">
         <is>
-          <t>science_dominant</t>
+          <t>swe_dominant</t>
         </is>
       </c>
       <c r="V50" s="3" t="inlineStr">
         <is>
-          <t>hard</t>
+          <t>easy</t>
         </is>
       </c>
       <c r="W50" s="3" t="inlineStr">
@@ -5375,27 +5379,27 @@
       </c>
       <c r="X50" s="3" t="inlineStr">
         <is>
-          <t>sufficient</t>
+          <t>insufficient</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>psi4/psi4</t>
+          <t>astropy/astropy</t>
         </is>
       </c>
       <c r="B51" s="2" t="n">
-        <v>2452</v>
+        <v>8006</v>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>Typo in left eigenvector beta in scf_response.py tdscf_excitations</t>
+          <t>Add the Planck18 (full mission) cosmological parameters</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/psi4/psi4/issues/2452</t>
+          <t>https://github.com/astropy/astropy/issues/8006</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -5409,14 +5413,18 @@
         </is>
       </c>
       <c r="G51" s="3" t="inlineStr"/>
-      <c r="H51" s="3" t="inlineStr"/>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>cosmology</t>
+        </is>
+      </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/psi4/psi4/pull/2453</t>
+          <t>https://github.com/astropy/astropy/pull/8111</t>
         </is>
       </c>
       <c r="J51" s="2" t="n">
-        <v>2453</v>
+        <v>8111</v>
       </c>
       <c r="K51" s="2" t="n"/>
       <c r="L51" s="2" t="n"/>
@@ -5433,7 +5441,7 @@
       </c>
       <c r="P51" s="3" t="inlineStr">
         <is>
-          <t>The PR patch changes the export variable for TD-LEFT EIGENVECTOR ALPHA to TD-LEFT EIGENVECTOR BETA and removes the overwriting/incorrect assignment of the alpha value with beta, aligning left eigenvector labels with the underlying L_eigvec indices.</t>
+          <t>The PR modifies astropy/cosmology/parameters.py to add a new Planck 2018 cosmology parameter dictionary (Planck18_arXiv_v2) with specified values and adds it to the available cosmologies list; it also updates CHANGES.rst to announce the addition.</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -5444,57 +5452,57 @@
       <c r="R51" s="3" t="inlineStr"/>
       <c r="S51" s="3" t="inlineStr">
         <is>
-          <t>The diff directly updates the specific variable name so that the stored left eigenvector uses the intended beta slot instead of overwriting the alpha slot.</t>
+          <t>The code addition introduces the Planck 2018 cosmological parameter values into the core cosmology parameters registry, enabling users to select them as a new named option.</t>
         </is>
       </c>
       <c r="T51" s="3" t="inlineStr">
         <is>
-          <t>Chemistry</t>
+          <t>Astronomy</t>
         </is>
       </c>
       <c r="U51" s="3" t="inlineStr">
         <is>
-          <t>swe_dominant</t>
+          <t>science_dominant</t>
         </is>
       </c>
       <c r="V51" s="3" t="inlineStr">
         <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="W51" s="3" t="inlineStr">
+        <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="W51" s="3" t="inlineStr">
-        <is>
-          <t>easy</t>
-        </is>
-      </c>
       <c r="X51" s="3" t="inlineStr">
         <is>
-          <t>insufficient</t>
+          <t>sufficient</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>psi4/psi4</t>
+          <t>astropy/astropy</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
-        <v>898</v>
+        <v>6044</v>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>mem requirement calculation in the dfocc module</t>
+          <t>Extraneous frame attribute mumbojumbo in StaticMatrixTransform</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/psi4/psi4/issues/898</t>
+          <t>https://github.com/astropy/astropy/issues/6044</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -5503,14 +5511,19 @@
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr"/>
-      <c r="H52" s="3" t="inlineStr"/>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>Bug
+coordinates</t>
+        </is>
+      </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/psi4/psi4/pull/1244</t>
+          <t>https://github.com/astropy/astropy/pull/6045</t>
         </is>
       </c>
       <c r="J52" s="2" t="n">
-        <v>1244</v>
+        <v>6045</v>
       </c>
       <c r="K52" s="2" t="n"/>
       <c r="L52" s="2" t="n"/>
@@ -5527,7 +5540,7 @@
       </c>
       <c r="P52" s="3" t="inlineStr">
         <is>
-          <t>The PR changes memory-estimation formulas in psi4/src/psi4/dfocc/manager.cc (and manager_cd.cc) from using nocc2AA/nocc2BB/nocc2AB to using naocc2AA/naocc2BB/naocc2AB, which directly incorporates the frozen-core-aware occupied counts into the amplitude memory requirement calculation referenced in the issue.</t>
+          <t>Removed code in StaticMatrixTransform.__call__ that computed overlapping_frame_attr_names from the input coordinate and passed them into toframe.realize_frame; now calls realize_frame(newrep) without propagating frame attributes, matching the reported fix title/body and CHANGES entry describing the erroneous attribute copying.</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -5538,12 +5551,12 @@
       <c r="R52" s="3" t="inlineStr"/>
       <c r="S52" s="3" t="inlineStr">
         <is>
-          <t>The requested fix is to ensure frozen-core is included in the DF-OCC memory estimation, and the implementation updates the relevant amplitude memory products to use the frozen-core-adjusted occupied dimensions (naocc* rather than nocc2*).</t>
+          <t>The patch directly removes the specific mechanism (propagating overlapping frame attributes) identified as extraneous in StaticMatrixTransform, aligning implementation with the stated bugfix.</t>
         </is>
       </c>
       <c r="T52" s="3" t="inlineStr">
         <is>
-          <t>Chemistry</t>
+          <t>Astronomy</t>
         </is>
       </c>
       <c r="U52" s="3" t="inlineStr">
@@ -5558,7 +5571,7 @@
       </c>
       <c r="W52" s="3" t="inlineStr">
         <is>
-          <t>easy</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="X52" s="3" t="inlineStr">
@@ -5570,20 +5583,20 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>obspy/obspy</t>
+          <t>astropy/astropy</t>
         </is>
       </c>
       <c r="B53" s="2" t="n">
-        <v>870</v>
+        <v>5611</v>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>Array analysis matplotlib date conversion bug</t>
+          <t>Flip output of make_rgb_lupton by default</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/obspy/obspy/issues/870</t>
+          <t>https://github.com/astropy/astropy/issues/5611</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -5599,17 +5612,16 @@
       <c r="G53" s="3" t="inlineStr"/>
       <c r="H53" s="3" t="inlineStr">
         <is>
-          <t>bug
-.signal</t>
+          <t>visualization</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/obspy/obspy/pull/956</t>
+          <t>https://github.com/astropy/astropy/pull/5612</t>
         </is>
       </c>
       <c r="J53" s="2" t="n">
-        <v>956</v>
+        <v>5612</v>
       </c>
       <c r="K53" s="2" t="n"/>
       <c r="L53" s="2" t="n"/>
@@ -5626,7 +5638,7 @@
       </c>
       <c r="P53" s="3" t="inlineStr">
         <is>
-          <t>The code change adjusts the mlabday conversion constant from adding 719162 hours between 1970 and 0001 to adding 719163 days between 1970 and 0001 (+1 epoch offset), aligning with the reported Rata Die epoch starting at 1 instead of 0.</t>
+          <t>The closing PR changed make_lupton_rgb’s PNG/JPEG saving path to call matplotlib.image.imsave(..., origin='lower') instead of the default, aligning image orientation with ds9 and fixing the previously reported vertical flip compared to FITS viewers.</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -5637,12 +5649,12 @@
       <c r="R53" s="3" t="inlineStr"/>
       <c r="S53" s="3" t="inlineStr">
         <is>
-          <t>The implementation directly applies the requested +1 correction to the mlabday numeric conversion used by array_processing.</t>
+          <t>The implementation directly addresses the reported mechanism (vertical origin/orientation mismatch) by setting the correct origin when writing raster images.</t>
         </is>
       </c>
       <c r="T53" s="3" t="inlineStr">
         <is>
-          <t>Earth Science</t>
+          <t>Astronomy</t>
         </is>
       </c>
       <c r="U53" s="3" t="inlineStr">
@@ -5669,20 +5681,20 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>astropy/astropy</t>
+          <t>deepchem/deepchem</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
-        <v>6391</v>
+        <v>1891</v>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>Wrong Earth radius</t>
+          <t>dc.metrics.balanced_accuracy_score is broken</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/astropy/astropy/issues/6391</t>
+          <t>https://github.com/deepchem/deepchem/issues/1891</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -5692,27 +5704,22 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G54" s="3" t="inlineStr">
-        <is>
-          <t>https://user-images.githubusercontent.com/316517/28540393-7f1ce650-70b5-11e7-85f5-e8901b7ae6ec.png</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr"/>
       <c r="H54" s="3" t="inlineStr">
         <is>
-          <t>Bug
-constants</t>
+          <t>bug</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/astropy/astropy/pull/6400</t>
+          <t>https://github.com/deepchem/deepchem/pull/1896</t>
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>6400</v>
+        <v>1896</v>
       </c>
       <c r="K54" s="2" t="n"/>
       <c r="L54" s="2" t="n"/>
@@ -5729,7 +5736,7 @@
       </c>
       <c r="P54" s="3" t="inlineStr">
         <is>
-          <t>The PR changes updated the IAU2015 Earth equatorial radius constant value from 6.3568e6 to 6.3781e6 and synchronized the `earthRad` unit/registry mappings accordingly, matching IAU 2015 Resolution B3’s nominal equatorial radius (while the issue reports the polar value was mistakenly used).</t>
+          <t>The change updates deepchem/metrics/__init__.py balanced_accuracy_score to call sklearn.metrics.balanced_accuracy_score with y, y_pred, and sample_weight=weights, aligning with the issue report that the previous line was broken.</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -5740,17 +5747,17 @@
       <c r="R54" s="3" t="inlineStr"/>
       <c r="S54" s="3" t="inlineStr">
         <is>
-          <t>The reported wrong-radius bug is caused by using the polar nominal value where the equatorial nominal value is expected, and the PR directly corrects both the constant and unit equivalence values to 6.3781e6 m.</t>
+          <t>The patch replaces the broken internal computation path with the correct sklearn balanced_accuracy_score call using the computed weights, which plausibly restores the metric’s correct behavior.</t>
         </is>
       </c>
       <c r="T54" s="3" t="inlineStr">
         <is>
-          <t>Astronomy</t>
+          <t>Chemistry</t>
         </is>
       </c>
       <c r="U54" s="3" t="inlineStr">
         <is>
-          <t>science_dominant</t>
+          <t>swe_dominant</t>
         </is>
       </c>
       <c r="V54" s="3" t="inlineStr">
@@ -5765,32 +5772,32 @@
       </c>
       <c r="X54" s="3" t="inlineStr">
         <is>
-          <t>sufficient</t>
+          <t>insufficient</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>astropy/astropy</t>
+          <t>qiskit/qiskit</t>
         </is>
       </c>
       <c r="B55" s="2" t="n">
-        <v>16526</v>
+        <v>16102</v>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>Missing prefixes for SI-Unit "Becquerel" in astropy.units</t>
+          <t>plot_bloch_vector modifies list input</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/astropy/astropy/issues/16526</t>
+          <t>https://github.com/Qiskit/qiskit/issues/16102</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -5801,17 +5808,16 @@
       <c r="G55" s="3" t="inlineStr"/>
       <c r="H55" s="3" t="inlineStr">
         <is>
-          <t>units
-Bug</t>
+          <t>bug</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/astropy/astropy/pull/16529</t>
+          <t>https://github.com/Qiskit/qiskit/pull/16103</t>
         </is>
       </c>
       <c r="J55" s="2" t="n">
-        <v>16529</v>
+        <v>16103</v>
       </c>
       <c r="K55" s="2" t="n"/>
       <c r="L55" s="2" t="n"/>
@@ -5828,7 +5834,7 @@
       </c>
       <c r="P55" s="3" t="inlineStr">
         <is>
-          <t>The PR changes `astropy/units/si.py` to set `prefixes=True` for the `Bq` (becquerel) and `Ci` (curie) unit definitions, changing them from `prefixes=False`; this directly enables SI-prefix generation (e.g., `u.MBq`) consistent with the issue’s expected behavior.</t>
+          <t>In plot_bloch_vector, the spherical-coordinate path previously wrote back into the input via bloch[0]=..., bloch[1]=..., bloch[2]=..., which mutates list inputs; the fix instead treats bloch as a tuple, destructures r, theta, phi, and creates a new (x, y, z) tuple for Bloch.add_vectors, avoiding mutation.</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -5839,7 +5845,7 @@
       <c r="R55" s="3" t="inlineStr"/>
       <c r="S55" s="3" t="inlineStr">
         <is>
-          <t>Enabling `prefixes=True` in the unit definitions is the targeted mechanism to make prefixed units like `MBq` available, matching the reported missing-attribute bug.</t>
+          <t>The change removes in-place assignment during spherical-to-Cartesian conversion, so list inputs are no longer mutated and tuple inputs are supported.</t>
         </is>
       </c>
       <c r="T55" s="3" t="inlineStr">
@@ -5849,7 +5855,7 @@
       </c>
       <c r="U55" s="3" t="inlineStr">
         <is>
-          <t>science_dominant</t>
+          <t>swe_dominant</t>
         </is>
       </c>
       <c r="V55" s="3" t="inlineStr">
@@ -5864,27 +5870,27 @@
       </c>
       <c r="X55" s="3" t="inlineStr">
         <is>
-          <t>sufficient</t>
+          <t>insufficient</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>astropy/astropy</t>
+          <t>qiskit/qiskit</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
-        <v>12518</v>
+        <v>15602</v>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>astropy.cosmology.utils.aszarr does not take Column object</t>
+          <t>Add equivalence for `XXMinusYY` to the equivalence library</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/astropy/astropy/issues/12518</t>
+          <t>https://github.com/Qiskit/qiskit/issues/15602</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -5899,699 +5905,6 @@
       </c>
       <c r="G56" s="3" t="inlineStr"/>
       <c r="H56" s="3" t="inlineStr">
-        <is>
-          <t>Bug
-cosmology</t>
-        </is>
-      </c>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/astropy/astropy/pull/12525</t>
-        </is>
-      </c>
-      <c r="J56" s="2" t="n">
-        <v>12525</v>
-      </c>
-      <c r="K56" s="2" t="n"/>
-      <c r="L56" s="2" t="n"/>
-      <c r="M56" s="3" t="inlineStr"/>
-      <c r="N56" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O56" s="2" t="inlineStr">
-        <is>
-          <t>direct_fix</t>
-        </is>
-      </c>
-      <c r="P56" s="3" t="inlineStr">
-        <is>
-          <t>The reported failure mode is that `aszarr` checks `hasattr(z, "unit")` and then calls `z.to_value(cu.redshift)`, which raises `AttributeError` for `astropy.table.Column` (Column has `unit` but no `to_value`). The closing PR modifies `astropy/cosmology/utils.py` so that when an object has `unit` (treated as Quantity/Column-like), it converts via an operation that works for both Quantity and Column: `(z &lt;&lt; cu.redshift).value` instead of `z.to_value(cu.redshift)`. The PR title/body explicitly states it fixes handling of `Column` objects for `astropy.cosmology.utils.aszarr`, and the code change targets the exact conversion path that previously called `to_value`.</t>
-        </is>
-      </c>
-      <c r="Q56" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="R56" s="3" t="inlineStr"/>
-      <c r="S56" s="3" t="inlineStr">
-        <is>
-          <t>The change replaces the Quantity-only `.to_value(cu.redshift)` call with a conversion expression that supports `Column` objects that provide `unit` but not `.to_value`, thereby preventing the reported `AttributeError` and producing redshift values consistently.</t>
-        </is>
-      </c>
-      <c r="T56" s="3" t="inlineStr">
-        <is>
-          <t>Astronomy</t>
-        </is>
-      </c>
-      <c r="U56" s="3" t="inlineStr">
-        <is>
-          <t>swe_dominant</t>
-        </is>
-      </c>
-      <c r="V56" s="3" t="inlineStr">
-        <is>
-          <t>easy</t>
-        </is>
-      </c>
-      <c r="W56" s="3" t="inlineStr">
-        <is>
-          <t>easy</t>
-        </is>
-      </c>
-      <c r="X56" s="3" t="inlineStr">
-        <is>
-          <t>insufficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>astropy/astropy</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="n">
-        <v>8006</v>
-      </c>
-      <c r="C57" s="3" t="inlineStr">
-        <is>
-          <t>Add the Planck18 (full mission) cosmological parameters</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/astropy/astropy/issues/8006</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G57" s="3" t="inlineStr"/>
-      <c r="H57" s="3" t="inlineStr">
-        <is>
-          <t>cosmology</t>
-        </is>
-      </c>
-      <c r="I57" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/astropy/astropy/pull/8111</t>
-        </is>
-      </c>
-      <c r="J57" s="2" t="n">
-        <v>8111</v>
-      </c>
-      <c r="K57" s="2" t="n"/>
-      <c r="L57" s="2" t="n"/>
-      <c r="M57" s="3" t="inlineStr"/>
-      <c r="N57" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O57" s="2" t="inlineStr">
-        <is>
-          <t>direct_fix</t>
-        </is>
-      </c>
-      <c r="P57" s="3" t="inlineStr">
-        <is>
-          <t>The PR modifies astropy/cosmology/parameters.py to add a new Planck 2018 cosmology parameter dictionary (Planck18_arXiv_v2) with specified values and adds it to the available cosmologies list; it also updates CHANGES.rst to announce the addition.</t>
-        </is>
-      </c>
-      <c r="Q57" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="R57" s="3" t="inlineStr"/>
-      <c r="S57" s="3" t="inlineStr">
-        <is>
-          <t>The code addition introduces the Planck 2018 cosmological parameter values into the core cosmology parameters registry, enabling users to select them as a new named option.</t>
-        </is>
-      </c>
-      <c r="T57" s="3" t="inlineStr">
-        <is>
-          <t>Astronomy</t>
-        </is>
-      </c>
-      <c r="U57" s="3" t="inlineStr">
-        <is>
-          <t>science_dominant</t>
-        </is>
-      </c>
-      <c r="V57" s="3" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="W57" s="3" t="inlineStr">
-        <is>
-          <t>easy</t>
-        </is>
-      </c>
-      <c r="X57" s="3" t="inlineStr">
-        <is>
-          <t>sufficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>astropy/astropy</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="n">
-        <v>6044</v>
-      </c>
-      <c r="C58" s="3" t="inlineStr">
-        <is>
-          <t>Extraneous frame attribute mumbojumbo in StaticMatrixTransform</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/astropy/astropy/issues/6044</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G58" s="3" t="inlineStr"/>
-      <c r="H58" s="3" t="inlineStr">
-        <is>
-          <t>Bug
-coordinates</t>
-        </is>
-      </c>
-      <c r="I58" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/astropy/astropy/pull/6045</t>
-        </is>
-      </c>
-      <c r="J58" s="2" t="n">
-        <v>6045</v>
-      </c>
-      <c r="K58" s="2" t="n"/>
-      <c r="L58" s="2" t="n"/>
-      <c r="M58" s="3" t="inlineStr"/>
-      <c r="N58" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O58" s="2" t="inlineStr">
-        <is>
-          <t>direct_fix</t>
-        </is>
-      </c>
-      <c r="P58" s="3" t="inlineStr">
-        <is>
-          <t>Removed code in StaticMatrixTransform.__call__ that computed overlapping_frame_attr_names from the input coordinate and passed them into toframe.realize_frame; now calls realize_frame(newrep) without propagating frame attributes, matching the reported fix title/body and CHANGES entry describing the erroneous attribute copying.</t>
-        </is>
-      </c>
-      <c r="Q58" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="R58" s="3" t="inlineStr"/>
-      <c r="S58" s="3" t="inlineStr">
-        <is>
-          <t>The patch directly removes the specific mechanism (propagating overlapping frame attributes) identified as extraneous in StaticMatrixTransform, aligning implementation with the stated bugfix.</t>
-        </is>
-      </c>
-      <c r="T58" s="3" t="inlineStr">
-        <is>
-          <t>Astronomy</t>
-        </is>
-      </c>
-      <c r="U58" s="3" t="inlineStr">
-        <is>
-          <t>joint</t>
-        </is>
-      </c>
-      <c r="V58" s="3" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="W58" s="3" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="X58" s="3" t="inlineStr">
-        <is>
-          <t>sufficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>astropy/astropy</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="n">
-        <v>5611</v>
-      </c>
-      <c r="C59" s="3" t="inlineStr">
-        <is>
-          <t>Flip output of make_rgb_lupton by default</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/astropy/astropy/issues/5611</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F59" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G59" s="3" t="inlineStr"/>
-      <c r="H59" s="3" t="inlineStr">
-        <is>
-          <t>visualization</t>
-        </is>
-      </c>
-      <c r="I59" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/astropy/astropy/pull/5612</t>
-        </is>
-      </c>
-      <c r="J59" s="2" t="n">
-        <v>5612</v>
-      </c>
-      <c r="K59" s="2" t="n"/>
-      <c r="L59" s="2" t="n"/>
-      <c r="M59" s="3" t="inlineStr"/>
-      <c r="N59" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O59" s="2" t="inlineStr">
-        <is>
-          <t>direct_fix</t>
-        </is>
-      </c>
-      <c r="P59" s="3" t="inlineStr">
-        <is>
-          <t>The closing PR changed make_lupton_rgb’s PNG/JPEG saving path to call matplotlib.image.imsave(..., origin='lower') instead of the default, aligning image orientation with ds9 and fixing the previously reported vertical flip compared to FITS viewers.</t>
-        </is>
-      </c>
-      <c r="Q59" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="R59" s="3" t="inlineStr"/>
-      <c r="S59" s="3" t="inlineStr">
-        <is>
-          <t>The implementation directly addresses the reported mechanism (vertical origin/orientation mismatch) by setting the correct origin when writing raster images.</t>
-        </is>
-      </c>
-      <c r="T59" s="3" t="inlineStr">
-        <is>
-          <t>Astronomy</t>
-        </is>
-      </c>
-      <c r="U59" s="3" t="inlineStr">
-        <is>
-          <t>swe_dominant</t>
-        </is>
-      </c>
-      <c r="V59" s="3" t="inlineStr">
-        <is>
-          <t>easy</t>
-        </is>
-      </c>
-      <c r="W59" s="3" t="inlineStr">
-        <is>
-          <t>easy</t>
-        </is>
-      </c>
-      <c r="X59" s="3" t="inlineStr">
-        <is>
-          <t>insufficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>deepchem/deepchem</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="n">
-        <v>1891</v>
-      </c>
-      <c r="C60" s="3" t="inlineStr">
-        <is>
-          <t>dc.metrics.balanced_accuracy_score is broken</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/deepchem/deepchem/issues/1891</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F60" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G60" s="3" t="inlineStr"/>
-      <c r="H60" s="3" t="inlineStr">
-        <is>
-          <t>bug</t>
-        </is>
-      </c>
-      <c r="I60" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/deepchem/deepchem/pull/1896</t>
-        </is>
-      </c>
-      <c r="J60" s="2" t="n">
-        <v>1896</v>
-      </c>
-      <c r="K60" s="2" t="n"/>
-      <c r="L60" s="2" t="n"/>
-      <c r="M60" s="3" t="inlineStr"/>
-      <c r="N60" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O60" s="2" t="inlineStr">
-        <is>
-          <t>direct_fix</t>
-        </is>
-      </c>
-      <c r="P60" s="3" t="inlineStr">
-        <is>
-          <t>The change updates deepchem/metrics/__init__.py balanced_accuracy_score to call sklearn.metrics.balanced_accuracy_score with y, y_pred, and sample_weight=weights, aligning with the issue report that the previous line was broken.</t>
-        </is>
-      </c>
-      <c r="Q60" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="R60" s="3" t="inlineStr"/>
-      <c r="S60" s="3" t="inlineStr">
-        <is>
-          <t>The patch replaces the broken internal computation path with the correct sklearn balanced_accuracy_score call using the computed weights, which plausibly restores the metric’s correct behavior.</t>
-        </is>
-      </c>
-      <c r="T60" s="3" t="inlineStr">
-        <is>
-          <t>Chemistry</t>
-        </is>
-      </c>
-      <c r="U60" s="3" t="inlineStr">
-        <is>
-          <t>swe_dominant</t>
-        </is>
-      </c>
-      <c r="V60" s="3" t="inlineStr">
-        <is>
-          <t>easy</t>
-        </is>
-      </c>
-      <c r="W60" s="3" t="inlineStr">
-        <is>
-          <t>easy</t>
-        </is>
-      </c>
-      <c r="X60" s="3" t="inlineStr">
-        <is>
-          <t>insufficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>qgis/QGIS</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="n">
-        <v>57815</v>
-      </c>
-      <c r="C61" s="3" t="inlineStr">
-        <is>
-          <t>SensorThings data provider fails to read Observations-&gt;phenomenon_time when it is not an interval</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/qgis/QGIS/issues/57815</t>
-        </is>
-      </c>
-      <c r="E61" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F61" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G61" s="3" t="inlineStr">
-        <is>
-          <t>https://github.com/qgis/QGIS/assets/13164312/ce00b914-1425-48e5-b11b-fb02df429b85
-https://github.com/qgis/QGIS/assets/13164312/c62b43e3-e8f5-4962-94d9-bd9365b02bb3</t>
-        </is>
-      </c>
-      <c r="H61" s="3" t="inlineStr">
-        <is>
-          <t>Bug</t>
-        </is>
-      </c>
-      <c r="I61" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/qgis/QGIS/pull/57840</t>
-        </is>
-      </c>
-      <c r="J61" s="2" t="n">
-        <v>57840</v>
-      </c>
-      <c r="K61" s="2" t="n"/>
-      <c r="L61" s="2" t="n"/>
-      <c r="M61" s="3" t="inlineStr"/>
-      <c r="N61" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O61" s="2" t="inlineStr">
-        <is>
-          <t>direct_fix</t>
-        </is>
-      </c>
-      <c r="P61" s="3" t="inlineStr">
-        <is>
-          <t>The patch changes SensorThings datetime-range parsing for phenomenonTime by removing the allowInstant special-casing and adding explicit handling so that when an instant datetime is received it is treated as a valid range with identical start/end values.</t>
-        </is>
-      </c>
-      <c r="Q61" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="R61" s="3" t="inlineStr"/>
-      <c r="S61" s="3" t="inlineStr">
-        <is>
-          <t>The change implements the intended domain-semantic interpretation that an observation’s phenomenonTime instant (single datetime) should be mapped to a time interval with start=end, avoiding NULLs.</t>
-        </is>
-      </c>
-      <c r="T61" s="3" t="inlineStr">
-        <is>
-          <t>Geographical Information Science</t>
-        </is>
-      </c>
-      <c r="U61" s="3" t="inlineStr">
-        <is>
-          <t>swe_dominant</t>
-        </is>
-      </c>
-      <c r="V61" s="3" t="inlineStr">
-        <is>
-          <t>easy</t>
-        </is>
-      </c>
-      <c r="W61" s="3" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="X61" s="3" t="inlineStr">
-        <is>
-          <t>insufficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>qiskit/qiskit</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="n">
-        <v>16102</v>
-      </c>
-      <c r="C62" s="3" t="inlineStr">
-        <is>
-          <t>plot_bloch_vector modifies list input</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/Qiskit/qiskit/issues/16102</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F62" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G62" s="3" t="inlineStr"/>
-      <c r="H62" s="3" t="inlineStr">
-        <is>
-          <t>bug</t>
-        </is>
-      </c>
-      <c r="I62" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/Qiskit/qiskit/pull/16103</t>
-        </is>
-      </c>
-      <c r="J62" s="2" t="n">
-        <v>16103</v>
-      </c>
-      <c r="K62" s="2" t="n"/>
-      <c r="L62" s="2" t="n"/>
-      <c r="M62" s="3" t="inlineStr"/>
-      <c r="N62" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O62" s="2" t="inlineStr">
-        <is>
-          <t>direct_fix</t>
-        </is>
-      </c>
-      <c r="P62" s="3" t="inlineStr">
-        <is>
-          <t>In plot_bloch_vector, the spherical-coordinate path previously wrote back into the input via bloch[0]=..., bloch[1]=..., bloch[2]=..., which mutates list inputs; the fix instead treats bloch as a tuple, destructures r, theta, phi, and creates a new (x, y, z) tuple for Bloch.add_vectors, avoiding mutation.</t>
-        </is>
-      </c>
-      <c r="Q62" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="R62" s="3" t="inlineStr"/>
-      <c r="S62" s="3" t="inlineStr">
-        <is>
-          <t>The change removes in-place assignment during spherical-to-Cartesian conversion, so list inputs are no longer mutated and tuple inputs are supported.</t>
-        </is>
-      </c>
-      <c r="T62" s="3" t="inlineStr">
-        <is>
-          <t>Physics</t>
-        </is>
-      </c>
-      <c r="U62" s="3" t="inlineStr">
-        <is>
-          <t>swe_dominant</t>
-        </is>
-      </c>
-      <c r="V62" s="3" t="inlineStr">
-        <is>
-          <t>easy</t>
-        </is>
-      </c>
-      <c r="W62" s="3" t="inlineStr">
-        <is>
-          <t>easy</t>
-        </is>
-      </c>
-      <c r="X62" s="3" t="inlineStr">
-        <is>
-          <t>insufficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>qiskit/qiskit</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="n">
-        <v>15602</v>
-      </c>
-      <c r="C63" s="3" t="inlineStr">
-        <is>
-          <t>Add equivalence for `XXMinusYY` to the equivalence library</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/Qiskit/qiskit/issues/15602</t>
-        </is>
-      </c>
-      <c r="E63" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F63" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G63" s="3" t="inlineStr"/>
-      <c r="H63" s="3" t="inlineStr">
         <is>
           <t>good first issue
 type: feature request
@@ -6601,13 +5914,706 @@
 mod: circuit</t>
         </is>
       </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/Qiskit/qiskit/pull/15604</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="n">
+        <v>15604</v>
+      </c>
+      <c r="K56" s="2" t="n"/>
+      <c r="L56" s="2" t="n"/>
+      <c r="M56" s="3" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>direct_fix</t>
+        </is>
+      </c>
+      <c r="P56" s="3" t="inlineStr">
+        <is>
+          <t>The PR adds a missing standard equivalence for `XXMinusYYGate` in `standard_equivalence_library.rs` using the decomposition `RZ(-β) → RXX(θ/2) → RYY(-θ/2) → RZ(β)`, matching the requested circuit form and directly extending the existing library coverage.</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R56" s="3" t="inlineStr"/>
+      <c r="S56" s="3" t="inlineStr">
+        <is>
+          <t>The code change directly implements the exact missing `XXMinusYY` equivalence using the stated RXX/RYY-based decomposition, thereby resolving the feature request.</t>
+        </is>
+      </c>
+      <c r="T56" s="3" t="inlineStr">
+        <is>
+          <t>Physics</t>
+        </is>
+      </c>
+      <c r="U56" s="3" t="inlineStr">
+        <is>
+          <t>science_dominant</t>
+        </is>
+      </c>
+      <c r="V56" s="3" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="W56" s="3" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="X56" s="3" t="inlineStr">
+        <is>
+          <t>sufficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>qiskit/qiskit</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="n">
+        <v>12167</v>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>Strange Behaviour of `sx` gate when defined inline in QASM</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/Qiskit/qiskit/issues/12167</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="inlineStr"/>
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t>bug
+mod: qasm3</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/Qiskit/qiskit/pull/12387</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="n">
+        <v>12387</v>
+      </c>
+      <c r="K57" s="2" t="n"/>
+      <c r="L57" s="2" t="n"/>
+      <c r="M57" s="3" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>direct_fix</t>
+        </is>
+      </c>
+      <c r="P57" s="3" t="inlineStr">
+        <is>
+          <t>The issue describes `sx` defined inline as `pow(1/2) @ x a;` producing a different result than using `include "stdgates.inc"`, and first comments attribute this to `pow(1/2)` being evaluated with integer math (becoming `pow(0)`). The PR patch updates `stdgates.inc` so that `sx` uses `pow(0.5) @ x a;`, and similarly updates other gates using `pow(1/2)` to use `0.5`, consistent with fixing the integer-division/evaluation ambiguity.</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R57" s="3" t="inlineStr"/>
+      <c r="S57" s="3" t="inlineStr">
+        <is>
+          <t>Changing the library’s `sx` definition from `pow(1/2)` to `pow(0.5)` directly addresses the reported integer-division evaluation problem and makes inline behavior match the included standard definition.</t>
+        </is>
+      </c>
+      <c r="T57" s="3" t="inlineStr">
+        <is>
+          <t>Physics</t>
+        </is>
+      </c>
+      <c r="U57" s="3" t="inlineStr">
+        <is>
+          <t>science_dominant</t>
+        </is>
+      </c>
+      <c r="V57" s="3" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="W57" s="3" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="X57" s="3" t="inlineStr">
+        <is>
+          <t>sufficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>qiskit/qiskit</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="n">
+        <v>8446</v>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>plot_state_hinton axis is misplaced.</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/Qiskit/qiskit/issues/8446</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="inlineStr"/>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>bug
+good first issue
+mod: visualization</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/Qiskit/qiskit/pull/8447</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="n">
+        <v>8447</v>
+      </c>
+      <c r="K58" s="2" t="n"/>
+      <c r="L58" s="2" t="n"/>
+      <c r="M58" s="3" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>direct_fix</t>
+        </is>
+      </c>
+      <c r="P58" s="3" t="inlineStr">
+        <is>
+          <t>The implementation change corrects the plotted axis behavior by using the correct axis object for the imaginary subplot (ax2) and applying consistent coordinate mapping for matrix-to-plot placement, plus fixes layout with fig.tight_layout; specifically it replaces ax1 set_xlim/set_ylim with ax2 and adjusts row label ordering and rectangle coordinates via plot_x/plot_y.</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R58" s="3" t="inlineStr"/>
+      <c r="S58" s="3" t="inlineStr">
+        <is>
+          <t>The reported malfunction is in how density-matrix entries are mapped to Hinton-plot coordinates and how subplot axes/ticks are configured, and the patch directly corrects those coordinate and axis assignments.</t>
+        </is>
+      </c>
+      <c r="T58" s="3" t="inlineStr">
+        <is>
+          <t>Physics</t>
+        </is>
+      </c>
+      <c r="U58" s="3" t="inlineStr">
+        <is>
+          <t>swe_dominant</t>
+        </is>
+      </c>
+      <c r="V58" s="3" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="W58" s="3" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="X58" s="3" t="inlineStr">
+        <is>
+          <t>insufficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>scverse/scanpy</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="n">
+        <v>2830</v>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>Unable to plot embedding after Scanpy release 1.9.7</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/scverse/scanpy/issues/2830</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G59" s="3" t="inlineStr"/>
+      <c r="H59" s="3" t="inlineStr"/>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/scverse/scanpy/pull/2832</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="n">
+        <v>2832</v>
+      </c>
+      <c r="K59" s="2" t="n"/>
+      <c r="L59" s="2" t="n"/>
+      <c r="M59" s="3" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>direct_fix</t>
+        </is>
+      </c>
+      <c r="P59" s="3" t="inlineStr">
+        <is>
+          <t>The reported error occurs in scanpy plotting palette validation for numpy 1.23, and the PR changes _validate_palette to compare numpy palettes using np.array_equal(_palette, adata.uns[color_key]) (instead of np.equal(...).all()) which matches the fix described as addressing old numpy array palette handling.</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R59" s="3" t="inlineStr"/>
+      <c r="S59" s="3" t="inlineStr">
+        <is>
+          <t>By switching the palette equality check to np.array_equal, the code avoids numpy-version-dependent behavior that can trigger the reported UFuncTypeError when determining whether an array palette has changed.</t>
+        </is>
+      </c>
+      <c r="T59" s="3" t="inlineStr">
+        <is>
+          <t>Bioinformatics</t>
+        </is>
+      </c>
+      <c r="U59" s="3" t="inlineStr">
+        <is>
+          <t>swe_dominant</t>
+        </is>
+      </c>
+      <c r="V59" s="3" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="W59" s="3" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="X59" s="3" t="inlineStr">
+        <is>
+          <t>insufficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>rdkit/rdkit</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="n">
+        <v>7989</v>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>Wrong SMARTS pattern in O-benzyl deprotection reaction</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/rdkit/rdkit/issues/7989</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G60" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/user-attachments/assets/0899ab60-e623-4aa1-9674-5d40a0c2e5b9
+https://github.com/user-attachments/assets/2601c659-18f2-49d7-b8fb-5cd0cda83ca3
+https://github.com/user-attachments/assets/bb914eab-7d12-4c96-848a-4e2a94b7a5a2</t>
+        </is>
+      </c>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/rdkit/rdkit/pull/7990</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="n">
+        <v>7990</v>
+      </c>
+      <c r="K60" s="2" t="n"/>
+      <c r="L60" s="2" t="n"/>
+      <c r="M60" s="3" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>direct_fix</t>
+        </is>
+      </c>
+      <c r="P60" s="3" t="inlineStr">
+        <is>
+          <t>The PR patch updates the benzyl (Bn) deprotection SMARTS from an aromatic/oxygen pattern missing the benzylic carbon to a corrected pattern including the [CH2] linker and corresponding product mapping.</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R60" s="3" t="inlineStr"/>
+      <c r="S60" s="3" t="inlineStr">
+        <is>
+          <t>The code change directly amends the benzyl deprotection SMARTS to include the missing benzylic [CH2] carbon, aligning the reaction substructure match with true benzyl ethers and preventing phenyl ether matches.</t>
+        </is>
+      </c>
+      <c r="T60" s="3" t="inlineStr">
+        <is>
+          <t>Chemistry</t>
+        </is>
+      </c>
+      <c r="U60" s="3" t="inlineStr">
+        <is>
+          <t>science_dominant</t>
+        </is>
+      </c>
+      <c r="V60" s="3" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="W60" s="3" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="X60" s="3" t="inlineStr">
+        <is>
+          <t>sufficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>rdkit/rdkit</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="n">
+        <v>3097</v>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>Reactions should not use strict implicit valence calculations</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/rdkit/rdkit/issues/3097</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G61" s="3" t="inlineStr"/>
+      <c r="H61" s="3" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/rdkit/rdkit/pull/3098</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="n">
+        <v>3098</v>
+      </c>
+      <c r="K61" s="2" t="n"/>
+      <c r="L61" s="2" t="n"/>
+      <c r="M61" s="3" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>direct_fix</t>
+        </is>
+      </c>
+      <c r="P61" s="3" t="inlineStr">
+        <is>
+          <t>ReactionRunner.cpp changes calcImplicitValence from strict mode (true) to non-strict mode (false) for product stereo updates, and a new regression test (testGithub3097) asserts RunReactants returns non-empty products for the reported SMARTS/input instead of failing with explicit valence error.</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R61" s="3" t="inlineStr"/>
+      <c r="S61" s="3" t="inlineStr">
+        <is>
+          <t>The patch directly targets the stated offending code path by turning off strict implicit valence calculation in reactions and adds a regression test for the minimal SMARTS example.</t>
+        </is>
+      </c>
+      <c r="T61" s="3" t="inlineStr">
+        <is>
+          <t>Chemistry</t>
+        </is>
+      </c>
+      <c r="U61" s="3" t="inlineStr">
+        <is>
+          <t>joint</t>
+        </is>
+      </c>
+      <c r="V61" s="3" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="W61" s="3" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="X61" s="3" t="inlineStr">
+        <is>
+          <t>sufficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>rdkit/rdkit</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>Cleanup step of sanitization sometimes sets undesired formal charges</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/rdkit/rdkit/issues/2020</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G62" s="3" t="inlineStr"/>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/rdkit/rdkit/pull/2021</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="n">
+        <v>2021</v>
+      </c>
+      <c r="K62" s="2" t="n"/>
+      <c r="L62" s="2" t="n"/>
+      <c r="M62" s="3" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>direct_fix</t>
+        </is>
+      </c>
+      <c r="P62" s="3" t="inlineStr">
+        <is>
+          <t>The fix changes halogenCleanup so the iodine atom’s positive formal charge is assigned only as the number of double bonds converted with corresponding negative formal charges on neighboring oxygen atoms (formalCharge incremented per such double bond, instead of ev/2). Added tests cover several iodine oxy compounds including the reported motif with expected iodine formal charge 0 for 'CC(=O)O[IH2](O)OC(C)=O'.</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R62" s="3" t="inlineStr"/>
+      <c r="S62" s="3" t="inlineStr">
+        <is>
+          <t>The PR directly addresses the reported sanitization/halogen cleanup mechanism by preventing erroneous iodine partial positive charge assignment except in the specific double-bond-plus-oxygen-negative-charge case, and it adds regression tests for the problematic and related hypervalent iodine SMILES.</t>
+        </is>
+      </c>
+      <c r="T62" s="3" t="inlineStr">
+        <is>
+          <t>Chemistry</t>
+        </is>
+      </c>
+      <c r="U62" s="3" t="inlineStr">
+        <is>
+          <t>science_dominant</t>
+        </is>
+      </c>
+      <c r="V62" s="3" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="W62" s="3" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="X62" s="3" t="inlineStr">
+        <is>
+          <t>sufficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>qiskit/qiskit</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="n">
+        <v>3412</v>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>Add zeroing of pulse widths as a settable flag</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/Qiskit/qiskit/issues/3412</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G63" s="3" t="inlineStr"/>
+      <c r="H63" s="3" t="inlineStr">
+        <is>
+          <t>type: enhancement
+good first issue
+mod: pulse</t>
+        </is>
+      </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/Qiskit/qiskit/pull/15604</t>
+          <t>https://github.com/Qiskit/qiskit/pull/3419</t>
         </is>
       </c>
       <c r="J63" s="2" t="n">
-        <v>15604</v>
+        <v>3419</v>
       </c>
       <c r="K63" s="2" t="n"/>
       <c r="L63" s="2" t="n"/>
@@ -6624,7 +6630,7 @@
       </c>
       <c r="P63" s="3" t="inlineStr">
         <is>
-          <t>The PR adds a missing standard equivalence for `XXMinusYYGate` in `standard_equivalence_library.rs` using the decomposition `RZ(-β) → RXX(θ/2) → RYY(-θ/2) → RZ(β)`, matching the requested circuit form and directly extending the existing library coverage.</t>
+          <t>The implementation adds a settable `zero_ends: bool = True` flag to discrete pulse constructors (`gaussian`, `sech`, `gaussian_square`, and `drag`) that controls whether first/last samples are zeroed (`zeroed_width=duration if zero_ends else None`) and whether amplitude is rescaled to preserve the specified `amp` (`rescale_amp=bool(zero_ends)`).</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -6635,7 +6641,7 @@
       <c r="R63" s="3" t="inlineStr"/>
       <c r="S63" s="3" t="inlineStr">
         <is>
-          <t>The code change directly implements the exact missing `XXMinusYY` equivalence using the stated RXX/RYY-based decomposition, thereby resolving the feature request.</t>
+          <t>The code directly implements optional endpoint zeroing (with amplitude preservation when enabled) for the specified pulse types, matching the requested enhancement.</t>
         </is>
       </c>
       <c r="T63" s="3" t="inlineStr">
@@ -6645,7 +6651,7 @@
       </c>
       <c r="U63" s="3" t="inlineStr">
         <is>
-          <t>science_dominant</t>
+          <t>joint</t>
         </is>
       </c>
       <c r="V63" s="3" t="inlineStr">
@@ -6671,16 +6677,16 @@
         </is>
       </c>
       <c r="B64" s="2" t="n">
-        <v>12167</v>
+        <v>844</v>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>Strange Behaviour of `sx` gate when defined inline in QASM</t>
+          <t>Interactive Qsphere shows black vectors</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/Qiskit/qiskit/issues/12167</t>
+          <t>https://github.com/Qiskit/qiskit/issues/844</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -6690,23 +6696,26 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G64" s="3" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G64" s="3" t="inlineStr">
+        <is>
+          <t>https://user-images.githubusercontent.com/1753426/44908490-f28f4d00-ad1b-11e8-9173-73a3ab25290f.png</t>
+        </is>
+      </c>
       <c r="H64" s="3" t="inlineStr">
         <is>
-          <t>bug
-mod: qasm3</t>
+          <t>type: enhancement</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/Qiskit/qiskit/pull/12387</t>
+          <t>https://github.com/Qiskit/qiskit/pull/845</t>
         </is>
       </c>
       <c r="J64" s="2" t="n">
-        <v>12387</v>
+        <v>845</v>
       </c>
       <c r="K64" s="2" t="n"/>
       <c r="L64" s="2" t="n"/>
@@ -6723,7 +6732,7 @@
       </c>
       <c r="P64" s="3" t="inlineStr">
         <is>
-          <t>The issue describes `sx` defined inline as `pow(1/2) @ x a;` producing a different result than using `include "stdgates.inc"`, and first comments attribute this to `pow(1/2)` being evaluated with integer math (becoming `pow(0)`). The PR patch updates `stdgates.inc` so that `sx` uses `pow(0.5) @ x a;`, and similarly updates other gates using `pow(1/2)` to use `0.5`, consistent with fixing the integer-division/evaluation ambiguity.</t>
+          <t>The change modifies the phase computation used for Qsphere color mapping: it wraps np.angle(state[i]) into a [0, 2π) range via (angle + 2π) % (2π), which prevents negative phases from producing the black color outcome described in the issue.</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -6734,7 +6743,7 @@
       <c r="R64" s="3" t="inlineStr"/>
       <c r="S64" s="3" t="inlineStr">
         <is>
-          <t>Changing the library’s `sx` definition from `pow(1/2)` to `pow(0.5)` directly addresses the reported integer-division evaluation problem and makes inline behavior match the included standard definition.</t>
+          <t>By normalizing the phase angle to a strictly nonnegative interval, the vectors’ phase-dependent color no longer hits the black/off-range case caused by negative angles.</t>
         </is>
       </c>
       <c r="T64" s="3" t="inlineStr">
@@ -6744,42 +6753,42 @@
       </c>
       <c r="U64" s="3" t="inlineStr">
         <is>
-          <t>science_dominant</t>
+          <t>swe_dominant</t>
         </is>
       </c>
       <c r="V64" s="3" t="inlineStr">
         <is>
-          <t>hard</t>
+          <t>easy</t>
         </is>
       </c>
       <c r="W64" s="3" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>easy</t>
         </is>
       </c>
       <c r="X64" s="3" t="inlineStr">
         <is>
-          <t>sufficient</t>
+          <t>insufficient</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>qiskit/qiskit</t>
+          <t>qutip/qutip</t>
         </is>
       </c>
       <c r="B65" s="2" t="n">
-        <v>8446</v>
+        <v>1057</v>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>plot_state_hinton axis is misplaced.</t>
+          <t>_check_ket_dims fails</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/Qiskit/qiskit/issues/8446</t>
+          <t>https://github.com/qutip/qutip/issues/1057</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -6795,37 +6804,24 @@
       <c r="G65" s="3" t="inlineStr"/>
       <c r="H65" s="3" t="inlineStr">
         <is>
-          <t>bug
-good first issue
-mod: visualization</t>
+          <t>BUG
+good first issue</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/Qiskit/qiskit/pull/8447</t>
+          <t>https://github.com/qutip/qutip/pull/1058</t>
         </is>
       </c>
       <c r="J65" s="2" t="n">
-        <v>8447</v>
-      </c>
-      <c r="K65" s="2" t="n"/>
-      <c r="L65" s="2" t="n"/>
+        <v>1058</v>
+      </c>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr"/>
       <c r="M65" s="3" t="inlineStr"/>
-      <c r="N65" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O65" s="2" t="inlineStr">
-        <is>
-          <t>direct_fix</t>
-        </is>
-      </c>
-      <c r="P65" s="3" t="inlineStr">
-        <is>
-          <t>The implementation change corrects the plotted axis behavior by using the correct axis object for the imaginary subplot (ax2) and applying consistent coordinate mapping for matrix-to-plot placement, plus fixes layout with fig.tight_layout; specifically it replaces ax1 set_xlim/set_ylim with ax2 and adjusts row label ordering and rectangle coordinates via plot_x/plot_y.</t>
-        </is>
-      </c>
+      <c r="N65" s="2" t="inlineStr"/>
+      <c r="O65" s="2" t="inlineStr"/>
+      <c r="P65" s="3" t="inlineStr"/>
       <c r="Q65" s="2" t="inlineStr">
         <is>
           <t>No</t>
@@ -6834,7 +6830,7 @@
       <c r="R65" s="3" t="inlineStr"/>
       <c r="S65" s="3" t="inlineStr">
         <is>
-          <t>The reported malfunction is in how density-matrix entries are mapped to Hinton-plot coordinates and how subplot axes/ticks are configured, and the patch directly corrects those coordinate and axis assignments.</t>
+          <t>The quantum tensor-dimension invariant gives a self-contained reproducer and precise mathematical oracle for random ket generation.</t>
         </is>
       </c>
       <c r="T65" s="3" t="inlineStr">
@@ -6866,20 +6862,20 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>scverse/scanpy</t>
+          <t>qutip/qutip</t>
         </is>
       </c>
       <c r="B66" s="2" t="n">
-        <v>2830</v>
+        <v>2822</v>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>Unable to plot embedding after Scanpy release 1.9.7</t>
+          <t>`LinAlgWarning: Matrix is singular` when calculating `fidelity` of pure state density matrices</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/scverse/scanpy/issues/2830</t>
+          <t>https://github.com/qutip/qutip/issues/2822</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -6896,30 +6892,18 @@
       <c r="H66" s="3" t="inlineStr"/>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/scverse/scanpy/pull/2832</t>
+          <t>https://github.com/qutip/qutip/pull/2826</t>
         </is>
       </c>
       <c r="J66" s="2" t="n">
-        <v>2832</v>
-      </c>
-      <c r="K66" s="2" t="n"/>
-      <c r="L66" s="2" t="n"/>
+        <v>2826</v>
+      </c>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr"/>
       <c r="M66" s="3" t="inlineStr"/>
-      <c r="N66" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O66" s="2" t="inlineStr">
-        <is>
-          <t>direct_fix</t>
-        </is>
-      </c>
-      <c r="P66" s="3" t="inlineStr">
-        <is>
-          <t>The reported error occurs in scanpy plotting palette validation for numpy 1.23, and the PR changes _validate_palette to compare numpy palettes using np.array_equal(_palette, adata.uns[color_key]) (instead of np.equal(...).all()) which matches the fix described as addressing old numpy array palette handling.</t>
-        </is>
-      </c>
+      <c r="N66" s="2" t="inlineStr"/>
+      <c r="O66" s="2" t="inlineStr"/>
+      <c r="P66" s="3" t="inlineStr"/>
       <c r="Q66" s="2" t="inlineStr">
         <is>
           <t>No</t>
@@ -6928,52 +6912,52 @@
       <c r="R66" s="3" t="inlineStr"/>
       <c r="S66" s="3" t="inlineStr">
         <is>
-          <t>By switching the palette equality check to np.array_equal, the code avoids numpy-version-dependent behavior that can trigger the reported UFuncTypeError when determining whether an array palette has changed.</t>
+          <t>The warning originates from a numerical linear-algebra operation (matrix square root / fidelity for PSD density matrices) that should remain well-defined for pure states, so the fix requires domain-algorithmic handling (e.g., spectral decomposition) to avoid singular-matrix warnings while preserving correct fidelity.</t>
         </is>
       </c>
       <c r="T66" s="3" t="inlineStr">
         <is>
-          <t>Bioinformatics</t>
+          <t>Physics</t>
         </is>
       </c>
       <c r="U66" s="3" t="inlineStr">
         <is>
-          <t>swe_dominant</t>
+          <t>joint</t>
         </is>
       </c>
       <c r="V66" s="3" t="inlineStr">
         <is>
-          <t>easy</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="W66" s="3" t="inlineStr">
         <is>
-          <t>easy</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="X66" s="3" t="inlineStr">
         <is>
-          <t>insufficient</t>
+          <t>sufficient</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>rdkit/rdkit</t>
+          <t>scverse/scanpy</t>
         </is>
       </c>
       <c r="B67" s="2" t="n">
-        <v>7989</v>
+        <v>1411</v>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>Wrong SMARTS pattern in O-benzyl deprotection reaction</t>
+          <t>sc.tl.marker_gene_overlap() give the same values to each cluster</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/rdkit/rdkit/issues/7989</t>
+          <t>https://github.com/scverse/scanpy/issues/1411</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -6988,42 +6972,24 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/user-attachments/assets/0899ab60-e623-4aa1-9674-5d40a0c2e5b9
-https://github.com/user-attachments/assets/2601c659-18f2-49d7-b8fb-5cd0cda83ca3
-https://github.com/user-attachments/assets/bb914eab-7d12-4c96-848a-4e2a94b7a5a2</t>
-        </is>
-      </c>
-      <c r="H67" s="3" t="inlineStr">
-        <is>
-          <t>bug</t>
-        </is>
-      </c>
+          <t>https://user-images.githubusercontent.com/57720451/92608724-029c7880-f2b6-11ea-9860-59c705183fb2.png</t>
+        </is>
+      </c>
+      <c r="H67" s="3" t="inlineStr"/>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/rdkit/rdkit/pull/7990</t>
+          <t>https://github.com/scverse/scanpy/pull/1464</t>
         </is>
       </c>
       <c r="J67" s="2" t="n">
-        <v>7990</v>
-      </c>
-      <c r="K67" s="2" t="n"/>
-      <c r="L67" s="2" t="n"/>
+        <v>1464</v>
+      </c>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr"/>
       <c r="M67" s="3" t="inlineStr"/>
-      <c r="N67" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O67" s="2" t="inlineStr">
-        <is>
-          <t>direct_fix</t>
-        </is>
-      </c>
-      <c r="P67" s="3" t="inlineStr">
-        <is>
-          <t>The PR patch updates the benzyl (Bn) deprotection SMARTS from an aromatic/oxygen pattern missing the benzylic carbon to a corrected pattern including the [CH2] linker and corresponding product mapping.</t>
-        </is>
-      </c>
+      <c r="N67" s="2" t="inlineStr"/>
+      <c r="O67" s="2" t="inlineStr"/>
+      <c r="P67" s="3" t="inlineStr"/>
       <c r="Q67" s="2" t="inlineStr">
         <is>
           <t>No</t>
@@ -7032,17 +6998,17 @@
       <c r="R67" s="3" t="inlineStr"/>
       <c r="S67" s="3" t="inlineStr">
         <is>
-          <t>The code change directly amends the benzyl deprotection SMARTS to include the missing benzylic [CH2] carbon, aligning the reaction substructure match with true benzyl ethers and preventing phenyl ether matches.</t>
+          <t>The bug is caused by the internal defaulting logic when `top_n_markers=None`, leading to an incorrect marker selection or overlap denominator so overlaps become constant across clusters instead of varying with the actually selected marker genes.</t>
         </is>
       </c>
       <c r="T67" s="3" t="inlineStr">
         <is>
-          <t>Chemistry</t>
+          <t>Bioinformatics</t>
         </is>
       </c>
       <c r="U67" s="3" t="inlineStr">
         <is>
-          <t>science_dominant</t>
+          <t>joint</t>
         </is>
       </c>
       <c r="V67" s="3" t="inlineStr">
@@ -7068,21 +7034,21 @@
         </is>
       </c>
       <c r="B68" s="2" t="n">
-        <v>3097</v>
+        <v>9229</v>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>Reactions should not use strict implicit valence calculations</t>
+          <t>Incorrect UFF Inversion term gradient for P/As/Sb/Bi centers</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/rdkit/rdkit/issues/3097</t>
+          <t>https://github.com/rdkit/rdkit/issues/9229</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -7098,30 +7064,18 @@
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/rdkit/rdkit/pull/3098</t>
+          <t>https://github.com/rdkit/rdkit/pull/9228</t>
         </is>
       </c>
       <c r="J68" s="2" t="n">
-        <v>3098</v>
-      </c>
-      <c r="K68" s="2" t="n"/>
-      <c r="L68" s="2" t="n"/>
+        <v>9228</v>
+      </c>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr"/>
       <c r="M68" s="3" t="inlineStr"/>
-      <c r="N68" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O68" s="2" t="inlineStr">
-        <is>
-          <t>direct_fix</t>
-        </is>
-      </c>
-      <c r="P68" s="3" t="inlineStr">
-        <is>
-          <t>ReactionRunner.cpp changes calcImplicitValence from strict mode (true) to non-strict mode (false) for product stereo updates, and a new regression test (testGithub3097) asserts RunReactants returns non-empty products for the reported SMARTS/input instead of failing with explicit valence error.</t>
-        </is>
-      </c>
+      <c r="N68" s="2" t="inlineStr"/>
+      <c r="O68" s="2" t="inlineStr"/>
+      <c r="P68" s="3" t="inlineStr"/>
       <c r="Q68" s="2" t="inlineStr">
         <is>
           <t>No</t>
@@ -7130,7 +7084,7 @@
       <c r="R68" s="3" t="inlineStr"/>
       <c r="S68" s="3" t="inlineStr">
         <is>
-          <t>The patch directly targets the stated offending code path by turning off strict implicit valence calculation in reactions and adds a regression test for the minimal SMARTS example.</t>
+          <t>The bug concerns the mathematical correctness of the analytical gradient of a UFF inversion energy term (sign of the C2 contribution), which is a domain-specific numerical derivative issue.</t>
         </is>
       </c>
       <c r="T68" s="3" t="inlineStr">
@@ -7140,759 +7094,20 @@
       </c>
       <c r="U68" s="3" t="inlineStr">
         <is>
-          <t>joint</t>
+          <t>science_dominant</t>
         </is>
       </c>
       <c r="V68" s="3" t="inlineStr">
         <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="W68" s="3" t="inlineStr">
+        <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="W68" s="3" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
       <c r="X68" s="3" t="inlineStr">
-        <is>
-          <t>sufficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>rdkit/rdkit</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="n">
-        <v>2020</v>
-      </c>
-      <c r="C69" s="3" t="inlineStr">
-        <is>
-          <t>Cleanup step of sanitization sometimes sets undesired formal charges</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/rdkit/rdkit/issues/2020</t>
-        </is>
-      </c>
-      <c r="E69" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F69" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G69" s="3" t="inlineStr"/>
-      <c r="H69" s="3" t="inlineStr">
-        <is>
-          <t>bug</t>
-        </is>
-      </c>
-      <c r="I69" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/rdkit/rdkit/pull/2021</t>
-        </is>
-      </c>
-      <c r="J69" s="2" t="n">
-        <v>2021</v>
-      </c>
-      <c r="K69" s="2" t="n"/>
-      <c r="L69" s="2" t="n"/>
-      <c r="M69" s="3" t="inlineStr"/>
-      <c r="N69" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O69" s="2" t="inlineStr">
-        <is>
-          <t>direct_fix</t>
-        </is>
-      </c>
-      <c r="P69" s="3" t="inlineStr">
-        <is>
-          <t>The fix changes halogenCleanup so the iodine atom’s positive formal charge is assigned only as the number of double bonds converted with corresponding negative formal charges on neighboring oxygen atoms (formalCharge incremented per such double bond, instead of ev/2). Added tests cover several iodine oxy compounds including the reported motif with expected iodine formal charge 0 for 'CC(=O)O[IH2](O)OC(C)=O'.</t>
-        </is>
-      </c>
-      <c r="Q69" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="R69" s="3" t="inlineStr"/>
-      <c r="S69" s="3" t="inlineStr">
-        <is>
-          <t>The PR directly addresses the reported sanitization/halogen cleanup mechanism by preventing erroneous iodine partial positive charge assignment except in the specific double-bond-plus-oxygen-negative-charge case, and it adds regression tests for the problematic and related hypervalent iodine SMILES.</t>
-        </is>
-      </c>
-      <c r="T69" s="3" t="inlineStr">
-        <is>
-          <t>Chemistry</t>
-        </is>
-      </c>
-      <c r="U69" s="3" t="inlineStr">
-        <is>
-          <t>science_dominant</t>
-        </is>
-      </c>
-      <c r="V69" s="3" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="W69" s="3" t="inlineStr">
-        <is>
-          <t>easy</t>
-        </is>
-      </c>
-      <c r="X69" s="3" t="inlineStr">
-        <is>
-          <t>sufficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>qgis/QGIS</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="n">
-        <v>30940</v>
-      </c>
-      <c r="C70" s="3" t="inlineStr">
-        <is>
-          <t>Allow inverting mouse wheel</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/qgis/QGIS/issues/30940</t>
-        </is>
-      </c>
-      <c r="E70" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F70" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G70" s="3" t="inlineStr"/>
-      <c r="H70" s="3" t="inlineStr">
-        <is>
-          <t>Feature Request</t>
-        </is>
-      </c>
-      <c r="I70" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/qgis/QGIS/pull/52303</t>
-        </is>
-      </c>
-      <c r="J70" s="2" t="n">
-        <v>52303</v>
-      </c>
-      <c r="K70" s="2" t="n"/>
-      <c r="L70" s="2" t="n"/>
-      <c r="M70" s="3" t="inlineStr"/>
-      <c r="N70" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O70" s="2" t="inlineStr">
-        <is>
-          <t>direct_fix</t>
-        </is>
-      </c>
-      <c r="P70" s="3" t="inlineStr">
-        <is>
-          <t>The change introduces a new boolean setting (/qgis/reverse_wheel_zoom) and, in wheelZoom handlers across multiple canvases/views (including QgsMapCanvas::wheelEvent), flips the sign interpretation of wheel delta (zoomIn is inverted when reverseZoom is enabled), then uses that to compute the scale factor applied during wheel zoom.</t>
-        </is>
-      </c>
-      <c r="Q70" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="R70" s="3" t="inlineStr"/>
-      <c r="S70" s="3" t="inlineStr">
-        <is>
-          <t>By directly inverting the wheel-delta-to-zoom-direction mapping used for wheel-based magnification, the implementation achieves the requested reverse wheel zoom behavior without changing unrelated non-wheel zoom tools.</t>
-        </is>
-      </c>
-      <c r="T70" s="3" t="inlineStr">
-        <is>
-          <t>Geographical Information Science</t>
-        </is>
-      </c>
-      <c r="U70" s="3" t="inlineStr">
-        <is>
-          <t>swe_dominant</t>
-        </is>
-      </c>
-      <c r="V70" s="3" t="inlineStr">
-        <is>
-          <t>easy</t>
-        </is>
-      </c>
-      <c r="W70" s="3" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="X70" s="3" t="inlineStr">
-        <is>
-          <t>insufficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>qiskit/qiskit</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="n">
-        <v>3412</v>
-      </c>
-      <c r="C71" s="3" t="inlineStr">
-        <is>
-          <t>Add zeroing of pulse widths as a settable flag</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/Qiskit/qiskit/issues/3412</t>
-        </is>
-      </c>
-      <c r="E71" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F71" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G71" s="3" t="inlineStr"/>
-      <c r="H71" s="3" t="inlineStr">
-        <is>
-          <t>type: enhancement
-good first issue
-mod: pulse</t>
-        </is>
-      </c>
-      <c r="I71" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/Qiskit/qiskit/pull/3419</t>
-        </is>
-      </c>
-      <c r="J71" s="2" t="n">
-        <v>3419</v>
-      </c>
-      <c r="K71" s="2" t="n"/>
-      <c r="L71" s="2" t="n"/>
-      <c r="M71" s="3" t="inlineStr"/>
-      <c r="N71" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O71" s="2" t="inlineStr">
-        <is>
-          <t>direct_fix</t>
-        </is>
-      </c>
-      <c r="P71" s="3" t="inlineStr">
-        <is>
-          <t>The implementation adds a settable `zero_ends: bool = True` flag to discrete pulse constructors (`gaussian`, `sech`, `gaussian_square`, and `drag`) that controls whether first/last samples are zeroed (`zeroed_width=duration if zero_ends else None`) and whether amplitude is rescaled to preserve the specified `amp` (`rescale_amp=bool(zero_ends)`).</t>
-        </is>
-      </c>
-      <c r="Q71" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="R71" s="3" t="inlineStr"/>
-      <c r="S71" s="3" t="inlineStr">
-        <is>
-          <t>The code directly implements optional endpoint zeroing (with amplitude preservation when enabled) for the specified pulse types, matching the requested enhancement.</t>
-        </is>
-      </c>
-      <c r="T71" s="3" t="inlineStr">
-        <is>
-          <t>Physics</t>
-        </is>
-      </c>
-      <c r="U71" s="3" t="inlineStr">
-        <is>
-          <t>joint</t>
-        </is>
-      </c>
-      <c r="V71" s="3" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="W71" s="3" t="inlineStr">
-        <is>
-          <t>easy</t>
-        </is>
-      </c>
-      <c r="X71" s="3" t="inlineStr">
-        <is>
-          <t>sufficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>qiskit/qiskit</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="n">
-        <v>844</v>
-      </c>
-      <c r="C72" s="3" t="inlineStr">
-        <is>
-          <t>Interactive Qsphere shows black vectors</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/Qiskit/qiskit/issues/844</t>
-        </is>
-      </c>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F72" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G72" s="3" t="inlineStr">
-        <is>
-          <t>https://user-images.githubusercontent.com/1753426/44908490-f28f4d00-ad1b-11e8-9173-73a3ab25290f.png</t>
-        </is>
-      </c>
-      <c r="H72" s="3" t="inlineStr">
-        <is>
-          <t>type: enhancement</t>
-        </is>
-      </c>
-      <c r="I72" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/Qiskit/qiskit/pull/845</t>
-        </is>
-      </c>
-      <c r="J72" s="2" t="n">
-        <v>845</v>
-      </c>
-      <c r="K72" s="2" t="n"/>
-      <c r="L72" s="2" t="n"/>
-      <c r="M72" s="3" t="inlineStr"/>
-      <c r="N72" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O72" s="2" t="inlineStr">
-        <is>
-          <t>direct_fix</t>
-        </is>
-      </c>
-      <c r="P72" s="3" t="inlineStr">
-        <is>
-          <t>The change modifies the phase computation used for Qsphere color mapping: it wraps np.angle(state[i]) into a [0, 2π) range via (angle + 2π) % (2π), which prevents negative phases from producing the black color outcome described in the issue.</t>
-        </is>
-      </c>
-      <c r="Q72" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="R72" s="3" t="inlineStr"/>
-      <c r="S72" s="3" t="inlineStr">
-        <is>
-          <t>By normalizing the phase angle to a strictly nonnegative interval, the vectors’ phase-dependent color no longer hits the black/off-range case caused by negative angles.</t>
-        </is>
-      </c>
-      <c r="T72" s="3" t="inlineStr">
-        <is>
-          <t>Physics</t>
-        </is>
-      </c>
-      <c r="U72" s="3" t="inlineStr">
-        <is>
-          <t>swe_dominant</t>
-        </is>
-      </c>
-      <c r="V72" s="3" t="inlineStr">
-        <is>
-          <t>easy</t>
-        </is>
-      </c>
-      <c r="W72" s="3" t="inlineStr">
-        <is>
-          <t>easy</t>
-        </is>
-      </c>
-      <c r="X72" s="3" t="inlineStr">
-        <is>
-          <t>insufficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t>qutip/qutip</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="n">
-        <v>1057</v>
-      </c>
-      <c r="C73" s="3" t="inlineStr">
-        <is>
-          <t>_check_ket_dims fails</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/qutip/qutip/issues/1057</t>
-        </is>
-      </c>
-      <c r="E73" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F73" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G73" s="3" t="inlineStr"/>
-      <c r="H73" s="3" t="inlineStr">
-        <is>
-          <t>BUG
-good first issue</t>
-        </is>
-      </c>
-      <c r="I73" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/qutip/qutip/pull/1058</t>
-        </is>
-      </c>
-      <c r="J73" s="2" t="n">
-        <v>1058</v>
-      </c>
-      <c r="K73" s="2" t="inlineStr"/>
-      <c r="L73" s="2" t="inlineStr"/>
-      <c r="M73" s="3" t="inlineStr"/>
-      <c r="N73" s="2" t="inlineStr"/>
-      <c r="O73" s="2" t="inlineStr"/>
-      <c r="P73" s="3" t="inlineStr"/>
-      <c r="Q73" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="R73" s="3" t="inlineStr"/>
-      <c r="S73" s="3" t="inlineStr">
-        <is>
-          <t>The quantum tensor-dimension invariant gives a self-contained reproducer and precise mathematical oracle for random ket generation.</t>
-        </is>
-      </c>
-      <c r="T73" s="3" t="inlineStr">
-        <is>
-          <t>Physics</t>
-        </is>
-      </c>
-      <c r="U73" s="3" t="inlineStr">
-        <is>
-          <t>swe_dominant</t>
-        </is>
-      </c>
-      <c r="V73" s="3" t="inlineStr">
-        <is>
-          <t>easy</t>
-        </is>
-      </c>
-      <c r="W73" s="3" t="inlineStr">
-        <is>
-          <t>easy</t>
-        </is>
-      </c>
-      <c r="X73" s="3" t="inlineStr">
-        <is>
-          <t>insufficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
-        <is>
-          <t>qutip/qutip</t>
-        </is>
-      </c>
-      <c r="B74" s="2" t="n">
-        <v>2822</v>
-      </c>
-      <c r="C74" s="3" t="inlineStr">
-        <is>
-          <t>`LinAlgWarning: Matrix is singular` when calculating `fidelity` of pure state density matrices</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/qutip/qutip/issues/2822</t>
-        </is>
-      </c>
-      <c r="E74" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F74" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G74" s="3" t="inlineStr"/>
-      <c r="H74" s="3" t="inlineStr"/>
-      <c r="I74" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/qutip/qutip/pull/2826</t>
-        </is>
-      </c>
-      <c r="J74" s="2" t="n">
-        <v>2826</v>
-      </c>
-      <c r="K74" s="2" t="inlineStr"/>
-      <c r="L74" s="2" t="inlineStr"/>
-      <c r="M74" s="3" t="inlineStr"/>
-      <c r="N74" s="2" t="inlineStr"/>
-      <c r="O74" s="2" t="inlineStr"/>
-      <c r="P74" s="3" t="inlineStr"/>
-      <c r="Q74" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="R74" s="3" t="inlineStr"/>
-      <c r="S74" s="3" t="inlineStr">
-        <is>
-          <t>The warning originates from a numerical linear-algebra operation (matrix square root / fidelity for PSD density matrices) that should remain well-defined for pure states, so the fix requires domain-algorithmic handling (e.g., spectral decomposition) to avoid singular-matrix warnings while preserving correct fidelity.</t>
-        </is>
-      </c>
-      <c r="T74" s="3" t="inlineStr">
-        <is>
-          <t>Physics</t>
-        </is>
-      </c>
-      <c r="U74" s="3" t="inlineStr">
-        <is>
-          <t>joint</t>
-        </is>
-      </c>
-      <c r="V74" s="3" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="W74" s="3" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="X74" s="3" t="inlineStr">
-        <is>
-          <t>sufficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
-        <is>
-          <t>scverse/scanpy</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="n">
-        <v>1411</v>
-      </c>
-      <c r="C75" s="3" t="inlineStr">
-        <is>
-          <t>sc.tl.marker_gene_overlap() give the same values to each cluster</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/scverse/scanpy/issues/1411</t>
-        </is>
-      </c>
-      <c r="E75" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F75" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G75" s="3" t="inlineStr">
-        <is>
-          <t>https://user-images.githubusercontent.com/57720451/92608724-029c7880-f2b6-11ea-9860-59c705183fb2.png</t>
-        </is>
-      </c>
-      <c r="H75" s="3" t="inlineStr"/>
-      <c r="I75" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/scverse/scanpy/pull/1464</t>
-        </is>
-      </c>
-      <c r="J75" s="2" t="n">
-        <v>1464</v>
-      </c>
-      <c r="K75" s="2" t="inlineStr"/>
-      <c r="L75" s="2" t="inlineStr"/>
-      <c r="M75" s="3" t="inlineStr"/>
-      <c r="N75" s="2" t="inlineStr"/>
-      <c r="O75" s="2" t="inlineStr"/>
-      <c r="P75" s="3" t="inlineStr"/>
-      <c r="Q75" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="R75" s="3" t="inlineStr"/>
-      <c r="S75" s="3" t="inlineStr">
-        <is>
-          <t>The bug is caused by the internal defaulting logic when `top_n_markers=None`, leading to an incorrect marker selection or overlap denominator so overlaps become constant across clusters instead of varying with the actually selected marker genes.</t>
-        </is>
-      </c>
-      <c r="T75" s="3" t="inlineStr">
-        <is>
-          <t>Bioinformatics</t>
-        </is>
-      </c>
-      <c r="U75" s="3" t="inlineStr">
-        <is>
-          <t>joint</t>
-        </is>
-      </c>
-      <c r="V75" s="3" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="W75" s="3" t="inlineStr">
-        <is>
-          <t>easy</t>
-        </is>
-      </c>
-      <c r="X75" s="3" t="inlineStr">
-        <is>
-          <t>sufficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>rdkit/rdkit</t>
-        </is>
-      </c>
-      <c r="B76" s="2" t="n">
-        <v>9229</v>
-      </c>
-      <c r="C76" s="3" t="inlineStr">
-        <is>
-          <t>Incorrect UFF Inversion term gradient for P/As/Sb/Bi centers</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/rdkit/rdkit/issues/9229</t>
-        </is>
-      </c>
-      <c r="E76" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F76" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G76" s="3" t="inlineStr"/>
-      <c r="H76" s="3" t="inlineStr">
-        <is>
-          <t>bug</t>
-        </is>
-      </c>
-      <c r="I76" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/rdkit/rdkit/pull/9228</t>
-        </is>
-      </c>
-      <c r="J76" s="2" t="n">
-        <v>9228</v>
-      </c>
-      <c r="K76" s="2" t="inlineStr"/>
-      <c r="L76" s="2" t="inlineStr"/>
-      <c r="M76" s="3" t="inlineStr"/>
-      <c r="N76" s="2" t="inlineStr"/>
-      <c r="O76" s="2" t="inlineStr"/>
-      <c r="P76" s="3" t="inlineStr"/>
-      <c r="Q76" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="R76" s="3" t="inlineStr"/>
-      <c r="S76" s="3" t="inlineStr">
-        <is>
-          <t>The bug concerns the mathematical correctness of the analytical gradient of a UFF inversion energy term (sign of the C2 contribution), which is a domain-specific numerical derivative issue.</t>
-        </is>
-      </c>
-      <c r="T76" s="3" t="inlineStr">
-        <is>
-          <t>Chemistry</t>
-        </is>
-      </c>
-      <c r="U76" s="3" t="inlineStr">
-        <is>
-          <t>science_dominant</t>
-        </is>
-      </c>
-      <c r="V76" s="3" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="W76" s="3" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="X76" s="3" t="inlineStr">
         <is>
           <t>sufficient</t>
         </is>
@@ -7941,11 +7156,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>82.7%</t>
+          <t>83.6%</t>
         </is>
       </c>
     </row>
@@ -7956,11 +7171,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>10.4%</t>
         </is>
       </c>
     </row>
@@ -7975,7 +7190,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>5.3%</t>
+          <t>6.0%</t>
         </is>
       </c>
     </row>
@@ -7986,7 +7201,7 @@
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>75</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>
